--- a/02_metabolome_leaf_processed_data.xlsx
+++ b/02_metabolome_leaf_processed_data.xlsx
@@ -1,32 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Metaboloma time course colonizacion bacteria\Leaf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marta\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6F0246-6C98-4578-B8CB-05EC9E3808AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381CB1F2-E575-49AC-9458-87ECB09AEC72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2C6FC011-A483-4EAB-8195-2486AC472A06}"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{2C6FC011-A483-4EAB-8195-2486AC472A06}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw data" sheetId="1" r:id="rId1"/>
-    <sheet name="Tabla dinamica completa" sheetId="11" r:id="rId2"/>
-    <sheet name="Tabla dinamica con superrutas" sheetId="13" r:id="rId3"/>
-    <sheet name="Subrutas" sheetId="14" r:id="rId4"/>
+    <sheet name="Dynamic table" sheetId="11" r:id="rId2"/>
+    <sheet name="Dynamic table processed" sheetId="13" r:id="rId3"/>
+    <sheet name="Subpathways" sheetId="14" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dynamic table'!$AM$3:$AM$105</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Raw data'!$A$2:$F$793</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Subrutas!$V$2:$V$92</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tabla dinamica completa'!$AM$3:$AM$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Subpathways!$V$2:$V$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId5"/>
-    <pivotCache cacheId="3" r:id="rId6"/>
+    <pivotCache cacheId="5" r:id="rId5"/>
+    <pivotCache cacheId="6" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2574" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2559" uniqueCount="224">
   <si>
     <t>Pathway</t>
   </si>
@@ -581,15 +581,6 @@
     <t>down</t>
   </si>
   <si>
-    <t>Early phase</t>
-  </si>
-  <si>
-    <t>Intermediate phase</t>
-  </si>
-  <si>
-    <t>Late phase</t>
-  </si>
-  <si>
     <t xml:space="preserve">y </t>
   </si>
   <si>
@@ -802,30 +793,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="15">
@@ -998,7 +971,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1045,27 +1018,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1158,7 +1124,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Tabla dinamica con superrutas'!$AK$46</c:f>
+              <c:f>'Dynamic table processed'!$AK$46</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1179,9 +1145,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Tabla dinamica con superrutas'!$AJ$47:$AJ$62</c:f>
+              <c:f>'Dynamic table processed'!$AJ$47:$AJ$61</c:f>
               <c:strCache>
-                <c:ptCount val="16"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>Membrane transport</c:v>
                 </c:pt>
@@ -1219,15 +1185,12 @@
                   <c:v>Carbohydrate metabolism</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>Glucosinolate biosynthesis</c:v>
+                  <c:v>Carbon metabolism</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Carbon metabolism</c:v>
+                  <c:v>Phenylpropanoid metabolism</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>Phenylpropanoid metabolism</c:v>
-                </c:pt>
-                <c:pt idx="15">
                   <c:v>Metabolism of cofactors and vitamins</c:v>
                 </c:pt>
               </c:strCache>
@@ -1235,10 +1198,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Tabla dinamica con superrutas'!$AK$47:$AK$62</c:f>
+              <c:f>'Dynamic table processed'!$AK$47:$AK$61</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -1276,15 +1239,12 @@
                   <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>7</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="15">
                   <c:v>17</c:v>
                 </c:pt>
               </c:numCache>
@@ -14138,7 +14098,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{71481A35-4629-4132-B7A7-47FFB654AF70}" name="TablaDinámica5" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{71481A35-4629-4132-B7A7-47FFB654AF70}" name="TablaDinámica5" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:AF105" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -14700,7 +14660,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85CC4EB8-6BBB-4642-9388-3152CB107A28}" name="TablaDinámica6" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85CC4EB8-6BBB-4642-9388-3152CB107A28}" name="TablaDinámica6" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:AF32" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
@@ -17981,7 +17941,7 @@
         <v>Amino acid metabolism</v>
       </c>
       <c r="I101" s="5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J101" t="s">
         <v>155</v>
@@ -18008,7 +17968,7 @@
         <v>Biosynthesis of phenylpropanoids</v>
       </c>
       <c r="I102" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="J102" t="s">
         <v>122</v>
@@ -18035,7 +17995,7 @@
         <v>Secondary metabolism</v>
       </c>
       <c r="I103" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J103" t="s">
         <v>119</v>
@@ -18062,10 +18022,10 @@
         <v>Phenylpropanoid metabolism</v>
       </c>
       <c r="I104" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J104" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.45">
@@ -18089,10 +18049,10 @@
         <v>Phenylpropanoid metabolism</v>
       </c>
       <c r="I105" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J105" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.45">
@@ -18116,10 +18076,10 @@
         <v>Phenylpropanoid metabolism</v>
       </c>
       <c r="I106" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J106" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.45">
@@ -18143,7 +18103,7 @@
         <v>Amino acid metabolism</v>
       </c>
       <c r="I107" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J107" t="s">
         <v>24</v>
@@ -18170,10 +18130,10 @@
         <v>Nucleotide metabolism</v>
       </c>
       <c r="I108" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J108" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.45">
@@ -18197,7 +18157,7 @@
         <v>Metabolism of cofactors and vitamins</v>
       </c>
       <c r="I109" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.45">
@@ -18221,7 +18181,7 @@
         <v>Terpenoid metabolism</v>
       </c>
       <c r="I110" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J110" t="s">
         <v>126</v>
@@ -18248,7 +18208,7 @@
         <v>Amino acid metabolism</v>
       </c>
       <c r="I111" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.45">
@@ -18272,7 +18232,7 @@
         <v>Degradation of aromatic compounds</v>
       </c>
       <c r="I112" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J112" t="s">
         <v>122</v>
@@ -18299,7 +18259,7 @@
         <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.45">
@@ -32630,16 +32590,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="AM1" s="22"/>
-      <c r="AN1" s="22"/>
-      <c r="AO1" s="22"/>
-      <c r="AP1" s="22"/>
-      <c r="AQ1" s="22"/>
-      <c r="AR1" s="22"/>
-      <c r="AS1" s="22"/>
-      <c r="AT1" s="22"/>
-      <c r="AU1" s="22"/>
-      <c r="AV1" s="22"/>
+      <c r="AM1" s="20"/>
+      <c r="AN1" s="20"/>
+      <c r="AO1" s="20"/>
+      <c r="AP1" s="20"/>
+      <c r="AQ1" s="20"/>
+      <c r="AR1" s="20"/>
+      <c r="AS1" s="20"/>
+      <c r="AT1" s="20"/>
+      <c r="AU1" s="20"/>
+      <c r="AV1" s="20"/>
     </row>
     <row r="3" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
@@ -33965,16 +33925,16 @@
       <c r="AG27" t="s">
         <v>127</v>
       </c>
-      <c r="AM27" s="22"/>
-      <c r="AN27" s="22"/>
-      <c r="AO27" s="22"/>
-      <c r="AP27" s="22"/>
-      <c r="AQ27" s="22"/>
-      <c r="AR27" s="22"/>
-      <c r="AS27" s="22"/>
-      <c r="AT27" s="22"/>
-      <c r="AU27" s="22"/>
-      <c r="AV27" s="22"/>
+      <c r="AM27" s="20"/>
+      <c r="AN27" s="20"/>
+      <c r="AO27" s="20"/>
+      <c r="AP27" s="20"/>
+      <c r="AQ27" s="20"/>
+      <c r="AR27" s="20"/>
+      <c r="AS27" s="20"/>
+      <c r="AT27" s="20"/>
+      <c r="AU27" s="20"/>
+      <c r="AV27" s="20"/>
     </row>
     <row r="28" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
@@ -37662,9 +37622,6 @@
       <c r="B3" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>141</v>
-      </c>
       <c r="AK3" t="s">
         <v>107</v>
       </c>
@@ -37734,46 +37691,46 @@
         <v>106</v>
       </c>
       <c r="AJ4" s="3"/>
-      <c r="AK4" s="24" t="s">
+      <c r="AK4" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="AL4" s="24"/>
-      <c r="AM4" s="24" t="s">
+      <c r="AL4" s="21"/>
+      <c r="AM4" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="AN4" s="24"/>
-      <c r="AO4" s="24" t="s">
+      <c r="AN4" s="21"/>
+      <c r="AO4" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="AP4" s="24"/>
-      <c r="AQ4" s="24" t="s">
+      <c r="AP4" s="21"/>
+      <c r="AQ4" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="AR4" s="24"/>
-      <c r="AS4" s="24" t="s">
+      <c r="AR4" s="21"/>
+      <c r="AS4" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="AT4" s="24"/>
-      <c r="AU4" s="24" t="s">
+      <c r="AT4" s="21"/>
+      <c r="AU4" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="AV4" s="24"/>
-      <c r="AW4" s="24" t="s">
+      <c r="AV4" s="21"/>
+      <c r="AW4" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="AX4" s="24"/>
-      <c r="AY4" s="24" t="s">
+      <c r="AX4" s="21"/>
+      <c r="AY4" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="AZ4" s="24"/>
-      <c r="BA4" s="24" t="s">
+      <c r="AZ4" s="21"/>
+      <c r="BA4" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="BB4" s="24"/>
-      <c r="BC4" s="24" t="s">
+      <c r="BB4" s="21"/>
+      <c r="BC4" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="BD4" s="24"/>
+      <c r="BD4" s="21"/>
     </row>
     <row r="5" spans="1:56" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
@@ -38775,42 +38732,38 @@
         <v>23</v>
       </c>
       <c r="AJ13" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="AK13" s="3"/>
-      <c r="AL13" s="3"/>
-      <c r="AM13" s="3">
-        <v>2</v>
-      </c>
+      <c r="AL13" s="3">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="3"/>
       <c r="AN13" s="3"/>
-      <c r="AO13" s="3">
-        <v>5</v>
-      </c>
+      <c r="AO13" s="3"/>
       <c r="AP13" s="3">
-        <v>4</v>
-      </c>
-      <c r="AQ13" s="3">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AQ13" s="3"/>
       <c r="AR13" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS13" s="3">
         <v>6</v>
       </c>
       <c r="AT13" s="3"/>
-      <c r="AU13" s="3"/>
+      <c r="AU13" s="3">
+        <v>1</v>
+      </c>
       <c r="AV13" s="3"/>
-      <c r="AW13" s="3">
-        <v>8</v>
-      </c>
+      <c r="AW13" s="3"/>
       <c r="AX13" s="3"/>
       <c r="AY13" s="3"/>
       <c r="AZ13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB13" s="3"/>
       <c r="BC13" s="3">
@@ -38903,45 +38856,57 @@
         <v>65</v>
       </c>
       <c r="AJ14" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AK14" s="3"/>
       <c r="AL14" s="3">
         <v>1</v>
       </c>
-      <c r="AM14" s="3"/>
-      <c r="AN14" s="3"/>
-      <c r="AO14" s="3"/>
+      <c r="AM14" s="3">
+        <v>2</v>
+      </c>
+      <c r="AN14" s="3">
+        <v>1</v>
+      </c>
+      <c r="AO14" s="3">
+        <v>10</v>
+      </c>
       <c r="AP14" s="3">
-        <v>2</v>
-      </c>
-      <c r="AQ14" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="AQ14" s="3">
+        <v>4</v>
+      </c>
       <c r="AR14" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS14" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="AT14" s="3"/>
       <c r="AU14" s="3">
-        <v>1</v>
-      </c>
-      <c r="AV14" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="AV14" s="3">
+        <v>6</v>
+      </c>
       <c r="AW14" s="3"/>
       <c r="AX14" s="3"/>
-      <c r="AY14" s="3"/>
-      <c r="AZ14" s="3">
-        <v>2</v>
-      </c>
+      <c r="AY14" s="3">
+        <v>5</v>
+      </c>
+      <c r="AZ14" s="3"/>
       <c r="BA14" s="3">
-        <v>1</v>
-      </c>
-      <c r="BB14" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="BB14" s="3">
+        <v>3</v>
+      </c>
       <c r="BC14" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:56" x14ac:dyDescent="0.45">
@@ -38985,57 +38950,57 @@
         <v>13</v>
       </c>
       <c r="AJ15" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="AK15" s="3"/>
+        <v>120</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>1</v>
+      </c>
       <c r="AL15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM15" s="3">
-        <v>2</v>
-      </c>
-      <c r="AN15" s="3">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AN15" s="3"/>
       <c r="AO15" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AP15" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AQ15" s="3">
-        <v>4</v>
-      </c>
-      <c r="AR15" s="3">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AR15" s="3"/>
       <c r="AS15" s="3">
-        <v>30</v>
-      </c>
-      <c r="AT15" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="AT15" s="3">
+        <v>1</v>
+      </c>
       <c r="AU15" s="3">
-        <v>2</v>
-      </c>
-      <c r="AV15" s="3">
-        <v>6</v>
-      </c>
-      <c r="AW15" s="3"/>
-      <c r="AX15" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="AV15" s="3"/>
+      <c r="AW15" s="3">
+        <v>2</v>
+      </c>
+      <c r="AX15" s="3">
+        <v>1</v>
+      </c>
       <c r="AY15" s="3">
-        <v>5</v>
-      </c>
-      <c r="AZ15" s="3"/>
-      <c r="BA15" s="3">
-        <v>2</v>
-      </c>
-      <c r="BB15" s="3">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AZ15" s="3">
+        <v>2</v>
+      </c>
+      <c r="BA15" s="3"/>
+      <c r="BB15" s="3"/>
       <c r="BC15" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="BD15" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:56" x14ac:dyDescent="0.45">
@@ -39085,57 +39050,67 @@
         <v>12</v>
       </c>
       <c r="AJ16" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AK16" s="3">
         <v>1</v>
       </c>
       <c r="AL16" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AM16" s="3">
         <v>1</v>
       </c>
-      <c r="AN16" s="3"/>
+      <c r="AN16" s="3">
+        <v>1</v>
+      </c>
       <c r="AO16" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AP16" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AQ16" s="3">
-        <v>2</v>
-      </c>
-      <c r="AR16" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="AR16" s="3">
+        <v>1</v>
+      </c>
       <c r="AS16" s="3">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AT16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU16" s="3">
-        <v>1</v>
-      </c>
-      <c r="AV16" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="AV16" s="3">
+        <v>8</v>
+      </c>
       <c r="AW16" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AX16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY16" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AZ16" s="3">
-        <v>2</v>
-      </c>
-      <c r="BA16" s="3"/>
-      <c r="BB16" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="BA16" s="3">
+        <v>7</v>
+      </c>
+      <c r="BB16" s="3">
+        <v>0</v>
+      </c>
       <c r="BC16" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="BD16" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:72" x14ac:dyDescent="0.45">
@@ -39203,43 +39178,43 @@
         <v>40</v>
       </c>
       <c r="AJ17" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="AK17" s="3">
         <v>1</v>
       </c>
       <c r="AL17" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AM17" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN17" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO17" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AP17" s="3">
+        <v>3</v>
+      </c>
+      <c r="AQ17" s="3">
+        <v>3</v>
+      </c>
+      <c r="AR17" s="3">
+        <v>2</v>
+      </c>
+      <c r="AS17" s="3">
+        <v>11</v>
+      </c>
+      <c r="AT17" s="3">
+        <v>1</v>
+      </c>
+      <c r="AU17" s="3">
         <v>5</v>
       </c>
-      <c r="AQ17" s="3">
-        <v>3</v>
-      </c>
-      <c r="AR17" s="3">
-        <v>1</v>
-      </c>
-      <c r="AS17" s="3">
-        <v>19</v>
-      </c>
-      <c r="AT17" s="3">
-        <v>2</v>
-      </c>
-      <c r="AU17" s="3">
-        <v>4</v>
-      </c>
       <c r="AV17" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AW17" s="3">
         <v>10</v>
@@ -39247,23 +39222,17 @@
       <c r="AX17" s="3">
         <v>2</v>
       </c>
-      <c r="AY17" s="3">
-        <v>6</v>
-      </c>
+      <c r="AY17" s="3"/>
       <c r="AZ17" s="3">
-        <v>3</v>
-      </c>
-      <c r="BA17" s="3">
-        <v>7</v>
-      </c>
-      <c r="BB17" s="3">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BA17" s="3"/>
+      <c r="BB17" s="3"/>
       <c r="BC17" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BD17" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:72" x14ac:dyDescent="0.45">
@@ -39325,61 +39294,67 @@
         <v>21</v>
       </c>
       <c r="AJ18" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AK18" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL18" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AM18" s="3">
         <v>2</v>
       </c>
       <c r="AN18" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO18" s="3">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="AP18" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AQ18" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AR18" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS18" s="3">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="AT18" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AU18" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AV18" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AW18" s="3">
+        <v>39</v>
+      </c>
+      <c r="AX18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AY18" s="3">
         <v>10</v>
       </c>
-      <c r="AX18" s="3">
-        <v>2</v>
-      </c>
-      <c r="AY18" s="3"/>
       <c r="AZ18" s="3">
-        <v>1</v>
-      </c>
-      <c r="BA18" s="3"/>
-      <c r="BB18" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="BA18" s="3">
+        <v>1</v>
+      </c>
+      <c r="BB18" s="3">
+        <v>1</v>
+      </c>
       <c r="BC18" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BD18" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:72" x14ac:dyDescent="0.45">
@@ -39462,68 +39437,36 @@
         <v>84</v>
       </c>
       <c r="AJ19" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="AK19" s="3">
-        <v>3</v>
-      </c>
-      <c r="AL19" s="3">
-        <v>5</v>
-      </c>
-      <c r="AM19" s="3">
-        <v>2</v>
-      </c>
-      <c r="AN19" s="3">
-        <v>0</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
       <c r="AO19" s="3">
-        <v>46</v>
-      </c>
-      <c r="AP19" s="3">
-        <v>10</v>
-      </c>
-      <c r="AQ19" s="3">
-        <v>13</v>
-      </c>
-      <c r="AR19" s="3">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
+      <c r="AR19" s="3"/>
       <c r="AS19" s="3">
-        <v>38</v>
-      </c>
-      <c r="AT19" s="3">
-        <v>6</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AT19" s="3"/>
       <c r="AU19" s="3">
-        <v>12</v>
-      </c>
-      <c r="AV19" s="3">
-        <v>9</v>
-      </c>
-      <c r="AW19" s="3">
-        <v>39</v>
-      </c>
-      <c r="AX19" s="3">
-        <v>0</v>
-      </c>
-      <c r="AY19" s="3">
-        <v>10</v>
-      </c>
-      <c r="AZ19" s="3">
-        <v>14</v>
-      </c>
-      <c r="BA19" s="3">
-        <v>1</v>
-      </c>
-      <c r="BB19" s="3">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AV19" s="3"/>
+      <c r="AW19" s="3"/>
+      <c r="AX19" s="3"/>
+      <c r="AY19" s="3"/>
+      <c r="AZ19" s="3"/>
+      <c r="BA19" s="3"/>
+      <c r="BB19" s="3"/>
       <c r="BC19" s="3">
-        <v>20</v>
-      </c>
-      <c r="BD19" s="3">
-        <v>4</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="BD19" s="3"/>
     </row>
     <row r="20" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
@@ -39605,36 +39548,68 @@
         <v>32</v>
       </c>
       <c r="AJ20" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="AK20" s="3"/>
-      <c r="AL20" s="3"/>
-      <c r="AM20" s="3"/>
-      <c r="AN20" s="3"/>
+        <v>136</v>
+      </c>
+      <c r="AK20" s="3">
+        <v>1</v>
+      </c>
+      <c r="AL20" s="3">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="3">
+        <v>2</v>
+      </c>
+      <c r="AN20" s="3">
+        <v>2</v>
+      </c>
       <c r="AO20" s="3">
-        <v>1</v>
-      </c>
-      <c r="AP20" s="3"/>
-      <c r="AQ20" s="3"/>
-      <c r="AR20" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="AP20" s="3">
+        <v>3</v>
+      </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR20" s="3">
+        <v>4</v>
+      </c>
       <c r="AS20" s="3">
-        <v>4</v>
-      </c>
-      <c r="AT20" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="AT20" s="3">
+        <v>0</v>
+      </c>
       <c r="AU20" s="3">
-        <v>1</v>
-      </c>
-      <c r="AV20" s="3"/>
-      <c r="AW20" s="3"/>
-      <c r="AX20" s="3"/>
-      <c r="AY20" s="3"/>
-      <c r="AZ20" s="3"/>
-      <c r="BA20" s="3"/>
-      <c r="BB20" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="AV20" s="3">
+        <v>5</v>
+      </c>
+      <c r="AW20" s="3">
+        <v>6</v>
+      </c>
+      <c r="AX20" s="3">
+        <v>1</v>
+      </c>
+      <c r="AY20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AZ20" s="3">
+        <v>2</v>
+      </c>
+      <c r="BA20" s="3">
+        <v>3</v>
+      </c>
+      <c r="BB20" s="3">
+        <v>0</v>
+      </c>
       <c r="BC20" s="3">
-        <v>2</v>
-      </c>
-      <c r="BD20" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="BD20" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
@@ -39688,69 +39663,6 @@
       <c r="AF21">
         <v>10</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AK21" s="3">
-        <v>1</v>
-      </c>
-      <c r="AL21" s="3">
-        <v>3</v>
-      </c>
-      <c r="AM21" s="3">
-        <v>2</v>
-      </c>
-      <c r="AN21" s="3">
-        <v>2</v>
-      </c>
-      <c r="AO21" s="3">
-        <v>8</v>
-      </c>
-      <c r="AP21" s="3">
-        <v>3</v>
-      </c>
-      <c r="AQ21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR21" s="3">
-        <v>4</v>
-      </c>
-      <c r="AS21" s="3">
-        <v>24</v>
-      </c>
-      <c r="AT21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AU21" s="3">
-        <v>3</v>
-      </c>
-      <c r="AV21" s="3">
-        <v>5</v>
-      </c>
-      <c r="AW21" s="3">
-        <v>6</v>
-      </c>
-      <c r="AX21" s="3">
-        <v>1</v>
-      </c>
-      <c r="AY21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AZ21" s="3">
-        <v>2</v>
-      </c>
-      <c r="BA21" s="3">
-        <v>3</v>
-      </c>
-      <c r="BB21" s="3">
-        <v>0</v>
-      </c>
-      <c r="BC21" s="3">
-        <v>8</v>
-      </c>
-      <c r="BD21" s="3">
-        <v>0</v>
-      </c>
     </row>
     <row r="22" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
@@ -40066,24 +39978,18 @@
         <v>43</v>
       </c>
       <c r="AJ25" t="s">
-        <v>181</v>
-      </c>
-      <c r="AK25" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL25" s="23"/>
-      <c r="AM25" s="23"/>
-      <c r="AN25" s="25" t="s">
-        <v>163</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="AK25" s="25"/>
+      <c r="AL25" s="25"/>
+      <c r="AM25" s="25"/>
+      <c r="AN25" s="25"/>
       <c r="AO25" s="25"/>
       <c r="AP25" s="25"/>
       <c r="AQ25" s="25"/>
-      <c r="AR25" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="AS25" s="26"/>
-      <c r="AT25" s="26"/>
+      <c r="AR25" s="25"/>
+      <c r="AS25" s="25"/>
+      <c r="AT25" s="25"/>
       <c r="AX25" t="s">
         <v>137</v>
       </c>
@@ -40099,9 +40005,9 @@
       <c r="BN25" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="BR25" s="3" t="s">
-        <v>136</v>
-      </c>
+      <c r="BR25" s="24"/>
+      <c r="BS25" s="24"/>
+      <c r="BT25" s="24"/>
     </row>
     <row r="26" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
@@ -40266,15 +40172,9 @@
       <c r="BP26" t="s">
         <v>160</v>
       </c>
-      <c r="BR26" t="s">
-        <v>159</v>
-      </c>
-      <c r="BS26" t="s">
-        <v>161</v>
-      </c>
-      <c r="BT26" t="s">
-        <v>160</v>
-      </c>
+      <c r="BR26" s="24"/>
+      <c r="BS26" s="24"/>
+      <c r="BT26" s="24"/>
     </row>
     <row r="27" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
@@ -40398,15 +40298,9 @@
       <c r="BP27" s="3">
         <v>1</v>
       </c>
-      <c r="BR27">
-        <v>1</v>
-      </c>
-      <c r="BS27" s="3">
-        <v>1</v>
-      </c>
-      <c r="BT27" s="3">
-        <v>3</v>
-      </c>
+      <c r="BR27" s="24"/>
+      <c r="BS27" s="24"/>
+      <c r="BT27" s="24"/>
     </row>
     <row r="28" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
@@ -40534,15 +40428,9 @@
       <c r="BP28" s="3">
         <v>2</v>
       </c>
-      <c r="BR28">
-        <v>2</v>
-      </c>
-      <c r="BS28" s="3">
-        <v>2</v>
-      </c>
-      <c r="BT28" s="3">
-        <v>2</v>
-      </c>
+      <c r="BR28" s="24"/>
+      <c r="BS28" s="24"/>
+      <c r="BT28" s="24"/>
     </row>
     <row r="29" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
@@ -40661,15 +40549,9 @@
       <c r="BP29" s="3">
         <v>3</v>
       </c>
-      <c r="BR29">
-        <v>3</v>
-      </c>
-      <c r="BS29" s="3">
-        <v>8</v>
-      </c>
-      <c r="BT29" s="3">
-        <v>3</v>
-      </c>
+      <c r="BR29" s="24"/>
+      <c r="BS29" s="24"/>
+      <c r="BT29" s="24"/>
     </row>
     <row r="30" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
@@ -40809,15 +40691,9 @@
       <c r="BP30" s="3">
         <v>2</v>
       </c>
-      <c r="BR30">
-        <v>4</v>
-      </c>
-      <c r="BS30" s="3">
-        <v>0</v>
-      </c>
-      <c r="BT30" s="3">
-        <v>4</v>
-      </c>
+      <c r="BR30" s="24"/>
+      <c r="BS30" s="24"/>
+      <c r="BT30" s="24"/>
     </row>
     <row r="31" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
@@ -40972,15 +40848,9 @@
       <c r="BP31" s="3">
         <v>1</v>
       </c>
-      <c r="BR31">
-        <v>5</v>
-      </c>
-      <c r="BS31" s="3">
-        <v>24</v>
-      </c>
-      <c r="BT31" s="3">
-        <v>0</v>
-      </c>
+      <c r="BR31" s="24"/>
+      <c r="BS31" s="24"/>
+      <c r="BT31" s="24"/>
     </row>
     <row r="32" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
@@ -41156,15 +41026,9 @@
       <c r="BP32" s="3">
         <v>4</v>
       </c>
-      <c r="BR32">
-        <v>6</v>
-      </c>
-      <c r="BS32" s="3">
-        <v>3</v>
-      </c>
-      <c r="BT32" s="3">
-        <v>5</v>
-      </c>
+      <c r="BR32" s="24"/>
+      <c r="BS32" s="24"/>
+      <c r="BT32" s="24"/>
     </row>
     <row r="33" spans="36:72" x14ac:dyDescent="0.45">
       <c r="AJ33" s="3" t="s">
@@ -41243,56 +41107,50 @@
       <c r="BP33" s="3">
         <v>2</v>
       </c>
-      <c r="BR33">
-        <v>7</v>
-      </c>
-      <c r="BS33" s="3">
-        <v>6</v>
-      </c>
-      <c r="BT33" s="3">
-        <v>1</v>
-      </c>
+      <c r="BR33" s="24"/>
+      <c r="BS33" s="24"/>
+      <c r="BT33" s="24"/>
     </row>
     <row r="34" spans="36:72" x14ac:dyDescent="0.45">
       <c r="AJ34" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="AK34" s="4">
+        <f>AL13-AK13</f>
+        <v>1</v>
+      </c>
+      <c r="AL34" s="4">
         <v>0</v>
       </c>
-      <c r="AL34" s="4">
-        <f t="shared" si="0"/>
-        <v>-2</v>
-      </c>
       <c r="AM34" s="4">
-        <f t="shared" si="1"/>
-        <v>-1</v>
+        <f>AP13-AO13</f>
+        <v>2</v>
       </c>
       <c r="AN34" s="4">
-        <f t="shared" si="2"/>
+        <f>AR13-AQ13</f>
         <v>1</v>
       </c>
       <c r="AO34" s="4">
-        <f t="shared" si="9"/>
+        <f>AT13-AS13</f>
         <v>-6</v>
       </c>
       <c r="AP34" s="4">
+        <f>AV13-AU13</f>
+        <v>-1</v>
+      </c>
+      <c r="AQ34" s="4">
         <v>0</v>
       </c>
-      <c r="AQ34" s="4">
-        <f t="shared" si="4"/>
-        <v>-8</v>
-      </c>
       <c r="AR34" s="4">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <f>AZ13-AY13</f>
+        <v>2</v>
       </c>
       <c r="AS34" s="4">
-        <f t="shared" si="6"/>
-        <v>-2</v>
+        <f>BB13-BA13</f>
+        <v>-1</v>
       </c>
       <c r="AT34" s="4">
-        <f t="shared" si="7"/>
+        <f>BD13-BC13</f>
         <v>-5</v>
       </c>
       <c r="AX34">
@@ -41332,57 +41190,52 @@
       <c r="BP34" s="3">
         <v>1</v>
       </c>
-      <c r="BR34">
-        <v>8</v>
-      </c>
-      <c r="BS34" s="3">
-        <v>0</v>
-      </c>
-      <c r="BT34" s="3">
-        <v>2</v>
-      </c>
+      <c r="BR34" s="24"/>
+      <c r="BS34" s="24"/>
+      <c r="BT34" s="24"/>
     </row>
     <row r="35" spans="36:72" x14ac:dyDescent="0.45">
       <c r="AJ35" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AK35" s="4">
-        <f t="shared" si="8"/>
+        <f>AL14-AK14</f>
         <v>1</v>
       </c>
       <c r="AL35" s="4">
-        <v>0</v>
+        <f>AN14-AM14</f>
+        <v>-1</v>
       </c>
       <c r="AM35" s="4">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f>AP14-AO14</f>
+        <v>-6</v>
       </c>
       <c r="AN35" s="4">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f>AR14-AQ14</f>
+        <v>-1</v>
       </c>
       <c r="AO35" s="4">
-        <f t="shared" si="9"/>
-        <v>-6</v>
+        <f>AT14-AS14</f>
+        <v>-30</v>
       </c>
       <c r="AP35" s="4">
-        <f t="shared" si="3"/>
-        <v>-1</v>
+        <f>AV14-AU14</f>
+        <v>4</v>
       </c>
       <c r="AQ35" s="4">
         <v>0</v>
       </c>
       <c r="AR35" s="4">
-        <f t="shared" si="5"/>
-        <v>2</v>
+        <f>AZ14-AY14</f>
+        <v>-5</v>
       </c>
       <c r="AS35" s="4">
-        <f t="shared" si="6"/>
-        <v>-1</v>
+        <f>BB14-BA14</f>
+        <v>1</v>
       </c>
       <c r="AT35" s="4">
-        <f t="shared" si="7"/>
-        <v>-5</v>
+        <f>BD14-BC14</f>
+        <v>-7</v>
       </c>
       <c r="AX35">
         <v>9</v>
@@ -41417,58 +41270,52 @@
       </c>
       <c r="BO35" s="3"/>
       <c r="BP35" s="3"/>
-      <c r="BR35">
-        <v>9</v>
-      </c>
-      <c r="BS35" s="3">
-        <v>3</v>
-      </c>
-      <c r="BT35" s="3">
-        <v>0</v>
-      </c>
+      <c r="BR35" s="24"/>
+      <c r="BS35" s="24"/>
+      <c r="BT35" s="24"/>
     </row>
     <row r="36" spans="36:72" x14ac:dyDescent="0.45">
       <c r="AJ36" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AK36" s="4">
-        <f t="shared" si="8"/>
+        <f>AL15-AK15</f>
         <v>1</v>
       </c>
       <c r="AL36" s="4">
-        <f t="shared" si="0"/>
+        <f>AN15-AM15</f>
         <v>-1</v>
       </c>
       <c r="AM36" s="4">
-        <f t="shared" si="1"/>
-        <v>-6</v>
+        <f>AP15-AO15</f>
+        <v>1</v>
       </c>
       <c r="AN36" s="4">
-        <f t="shared" si="2"/>
-        <v>-1</v>
+        <f>AR15-AQ15</f>
+        <v>-2</v>
       </c>
       <c r="AO36" s="4">
-        <f t="shared" si="9"/>
-        <v>-30</v>
+        <f>AT15-AS15</f>
+        <v>-10</v>
       </c>
       <c r="AP36" s="4">
-        <f t="shared" si="3"/>
-        <v>4</v>
+        <f>AV15-AU15</f>
+        <v>-1</v>
       </c>
       <c r="AQ36" s="4">
+        <f>AX15-AW15</f>
+        <v>-1</v>
+      </c>
+      <c r="AR36" s="4">
+        <f>AZ15-AY15</f>
+        <v>1</v>
+      </c>
+      <c r="AS36" s="4">
         <v>0</v>
       </c>
-      <c r="AR36" s="4">
-        <f t="shared" si="5"/>
-        <v>-5</v>
-      </c>
-      <c r="AS36" s="4">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
       <c r="AT36" s="4">
-        <f t="shared" si="7"/>
-        <v>-7</v>
+        <f>BD15-BC15</f>
+        <v>2</v>
       </c>
       <c r="AX36">
         <v>10</v>
@@ -41511,188 +41358,177 @@
       <c r="BP36" s="3">
         <v>2</v>
       </c>
-      <c r="BR36">
-        <v>10</v>
-      </c>
-      <c r="BS36" s="3">
-        <v>8</v>
-      </c>
-      <c r="BT36" s="3">
-        <v>0</v>
-      </c>
+      <c r="BR36" s="24"/>
+      <c r="BS36" s="24"/>
+      <c r="BT36" s="24"/>
     </row>
     <row r="37" spans="36:72" x14ac:dyDescent="0.45">
       <c r="AJ37" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AK37" s="4">
-        <f t="shared" si="8"/>
-        <v>1</v>
+        <f>AL16-AK16</f>
+        <v>5</v>
       </c>
       <c r="AL37" s="4">
-        <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM37" s="4">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>AP16-AO16</f>
+        <v>-5</v>
       </c>
       <c r="AN37" s="4">
-        <f t="shared" si="2"/>
+        <f>AR16-AQ16</f>
         <v>-2</v>
       </c>
       <c r="AO37" s="4">
-        <f t="shared" si="9"/>
-        <v>-10</v>
+        <f>AT16-AS16</f>
+        <v>-17</v>
       </c>
       <c r="AP37" s="4">
-        <f t="shared" si="3"/>
-        <v>-1</v>
+        <f>AV16-AU16</f>
+        <v>4</v>
       </c>
       <c r="AQ37" s="4">
-        <f t="shared" si="4"/>
-        <v>-1</v>
+        <f>AX16-AW16</f>
+        <v>-8</v>
       </c>
       <c r="AR37" s="4">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <f>AZ16-AY16</f>
+        <v>-3</v>
       </c>
       <c r="AS37" s="4">
-        <v>0</v>
+        <f>BB16-BA16</f>
+        <v>-7</v>
       </c>
       <c r="AT37" s="4">
-        <f t="shared" si="7"/>
-        <v>2</v>
+        <f>BD16-BC16</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="38" spans="36:72" x14ac:dyDescent="0.45">
       <c r="AJ38" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="AK38" s="4">
-        <f t="shared" si="8"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL38" s="4">
         <v>0</v>
       </c>
       <c r="AM38" s="4">
-        <f t="shared" si="1"/>
-        <v>-5</v>
+        <f>AP17-AO17</f>
+        <v>-4</v>
       </c>
       <c r="AN38" s="4">
-        <f t="shared" si="2"/>
-        <v>-2</v>
+        <f>AR17-AQ17</f>
+        <v>-1</v>
       </c>
       <c r="AO38" s="4">
-        <f t="shared" si="9"/>
-        <v>-17</v>
+        <f>AT17-AS17</f>
+        <v>-10</v>
       </c>
       <c r="AP38" s="4">
-        <f t="shared" si="3"/>
-        <v>4</v>
+        <f>AV17-AU17</f>
+        <v>-1</v>
       </c>
       <c r="AQ38" s="4">
-        <f t="shared" si="4"/>
+        <f>AX17-AW17</f>
         <v>-8</v>
       </c>
       <c r="AR38" s="4">
-        <f t="shared" si="5"/>
-        <v>-3</v>
+        <f>AZ17-AY17</f>
+        <v>1</v>
       </c>
       <c r="AS38" s="4">
-        <f t="shared" si="6"/>
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="AT38" s="4">
-        <f t="shared" si="7"/>
-        <v>-5</v>
+        <f>BD17-BC17</f>
+        <v>-8</v>
       </c>
     </row>
     <row r="39" spans="36:72" x14ac:dyDescent="0.45">
       <c r="AJ39" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AK39" s="4">
-        <v>0</v>
+        <f>AL18-AK18</f>
+        <v>2</v>
       </c>
       <c r="AL39" s="4">
-        <v>0</v>
+        <f>AN18-AM18</f>
+        <v>-2</v>
       </c>
       <c r="AM39" s="4">
-        <f t="shared" si="1"/>
-        <v>-4</v>
+        <f>AP18-AO18</f>
+        <v>-36</v>
       </c>
       <c r="AN39" s="4">
-        <f t="shared" si="2"/>
-        <v>-1</v>
+        <f>AR18-AQ18</f>
+        <v>-13</v>
       </c>
       <c r="AO39" s="4">
-        <f t="shared" si="9"/>
-        <v>-10</v>
+        <f>AT18-AS18</f>
+        <v>-32</v>
       </c>
       <c r="AP39" s="4">
-        <f t="shared" si="3"/>
-        <v>-1</v>
+        <f>AV18-AU18</f>
+        <v>-3</v>
       </c>
       <c r="AQ39" s="4">
-        <f t="shared" si="4"/>
-        <v>-8</v>
+        <f>AX18-AW18</f>
+        <v>-39</v>
       </c>
       <c r="AR39" s="4">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <f>AZ18-AY18</f>
+        <v>4</v>
       </c>
       <c r="AS39" s="4">
         <v>0</v>
       </c>
       <c r="AT39" s="4">
-        <f t="shared" si="7"/>
-        <v>-8</v>
+        <f>BD18-BC18</f>
+        <v>-16</v>
       </c>
     </row>
     <row r="40" spans="36:72" x14ac:dyDescent="0.45">
       <c r="AJ40" s="3" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="AK40" s="4">
-        <f t="shared" si="8"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL40" s="4">
-        <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AM40" s="4">
-        <f t="shared" si="1"/>
-        <v>-36</v>
+        <f>AP19-AO19</f>
+        <v>-1</v>
       </c>
       <c r="AN40" s="4">
-        <f t="shared" si="2"/>
-        <v>-13</v>
+        <v>0</v>
       </c>
       <c r="AO40" s="4">
-        <f t="shared" si="9"/>
-        <v>-32</v>
+        <f>AT19-AS19</f>
+        <v>-4</v>
       </c>
       <c r="AP40" s="4">
-        <f t="shared" si="3"/>
-        <v>-3</v>
+        <f>AV19-AU19</f>
+        <v>-1</v>
       </c>
       <c r="AQ40" s="4">
-        <f t="shared" si="4"/>
-        <v>-39</v>
+        <v>0</v>
       </c>
       <c r="AR40" s="4">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AS40" s="4">
         <v>0</v>
       </c>
       <c r="AT40" s="4">
-        <f t="shared" si="7"/>
-        <v>-16</v>
+        <f>BD19-BC19</f>
+        <v>-2</v>
       </c>
       <c r="AX40" s="3" t="s">
         <v>119</v>
@@ -41701,7 +41537,7 @@
         <v>129</v>
       </c>
       <c r="BF40" s="3" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="BJ40" s="3" t="s">
         <v>120</v>
@@ -41712,41 +41548,46 @@
     </row>
     <row r="41" spans="36:72" x14ac:dyDescent="0.45">
       <c r="AJ41" s="3" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="AK41" s="4">
-        <v>0</v>
+        <f>AL20-AK20</f>
+        <v>2</v>
       </c>
       <c r="AL41" s="4">
         <v>0</v>
       </c>
       <c r="AM41" s="4">
-        <f t="shared" si="1"/>
-        <v>-1</v>
+        <f>AP20-AO20</f>
+        <v>-5</v>
       </c>
       <c r="AN41" s="4">
-        <v>0</v>
+        <f>AR20-AQ20</f>
+        <v>4</v>
       </c>
       <c r="AO41" s="4">
-        <f t="shared" si="9"/>
-        <v>-4</v>
+        <f>AT20-AS20</f>
+        <v>-24</v>
       </c>
       <c r="AP41" s="4">
-        <f t="shared" si="3"/>
-        <v>-1</v>
+        <f>AV20-AU20</f>
+        <v>2</v>
       </c>
       <c r="AQ41" s="4">
-        <v>0</v>
+        <f>AX20-AW20</f>
+        <v>-5</v>
       </c>
       <c r="AR41" s="4">
-        <v>0</v>
+        <f>AZ20-AY20</f>
+        <v>2</v>
       </c>
       <c r="AS41" s="4">
-        <v>0</v>
+        <f>BB20-BA20</f>
+        <v>-3</v>
       </c>
       <c r="AT41" s="4">
-        <f t="shared" si="7"/>
-        <v>-2</v>
+        <f>BD20-BC20</f>
+        <v>-8</v>
       </c>
       <c r="AX41" t="s">
         <v>159</v>
@@ -41795,48 +41636,6 @@
       </c>
     </row>
     <row r="42" spans="36:72" x14ac:dyDescent="0.45">
-      <c r="AJ42" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AK42" s="4">
-        <f t="shared" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="AL42" s="4">
-        <v>0</v>
-      </c>
-      <c r="AM42" s="4">
-        <f t="shared" si="1"/>
-        <v>-5</v>
-      </c>
-      <c r="AN42" s="4">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="AO42" s="4">
-        <f t="shared" si="9"/>
-        <v>-24</v>
-      </c>
-      <c r="AP42" s="4">
-        <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="AQ42" s="4">
-        <f t="shared" si="4"/>
-        <v>-5</v>
-      </c>
-      <c r="AR42" s="4">
-        <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="AS42" s="4">
-        <f t="shared" si="6"/>
-        <v>-3</v>
-      </c>
-      <c r="AT42" s="4">
-        <f t="shared" si="7"/>
-        <v>-8</v>
-      </c>
       <c r="AX42">
         <v>1</v>
       </c>
@@ -41856,8 +41655,12 @@
       <c r="BF42">
         <v>1</v>
       </c>
-      <c r="BG42" s="3"/>
-      <c r="BH42" s="3"/>
+      <c r="BG42" s="3">
+        <v>1</v>
+      </c>
+      <c r="BH42" s="3">
+        <v>3</v>
+      </c>
       <c r="BJ42">
         <v>1</v>
       </c>
@@ -41900,7 +41703,9 @@
       <c r="BG43" s="3">
         <v>2</v>
       </c>
-      <c r="BH43" s="3"/>
+      <c r="BH43" s="3">
+        <v>2</v>
+      </c>
       <c r="BJ43">
         <v>2</v>
       </c>
@@ -41941,10 +41746,10 @@
         <v>3</v>
       </c>
       <c r="BG44" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BH44" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BJ44">
         <v>3</v>
@@ -41988,10 +41793,10 @@
         <v>4</v>
       </c>
       <c r="BG45" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH45" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BJ45">
         <v>4</v>
@@ -42039,9 +41844,11 @@
         <v>5</v>
       </c>
       <c r="BG46" s="3">
-        <v>6</v>
-      </c>
-      <c r="BH46" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="BH46" s="3">
+        <v>0</v>
+      </c>
       <c r="BJ46">
         <v>5</v>
       </c>
@@ -42092,8 +41899,12 @@
       <c r="BF47">
         <v>6</v>
       </c>
-      <c r="BG47" s="3"/>
-      <c r="BH47" s="3"/>
+      <c r="BG47" s="3">
+        <v>3</v>
+      </c>
+      <c r="BH47" s="3">
+        <v>5</v>
+      </c>
       <c r="BJ47">
         <v>6</v>
       </c>
@@ -42143,9 +41954,11 @@
         <v>7</v>
       </c>
       <c r="BG48" s="3">
-        <v>8</v>
-      </c>
-      <c r="BH48" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="BH48" s="3">
+        <v>1</v>
+      </c>
       <c r="BJ48">
         <v>7</v>
       </c>
@@ -42196,9 +42009,11 @@
       <c r="BF49">
         <v>8</v>
       </c>
-      <c r="BG49" s="3"/>
+      <c r="BG49" s="3">
+        <v>0</v>
+      </c>
       <c r="BH49" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ49">
         <v>8</v>
@@ -42245,9 +42060,11 @@
         <v>9</v>
       </c>
       <c r="BG50" s="3">
-        <v>2</v>
-      </c>
-      <c r="BH50" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="BH50" s="3">
+        <v>0</v>
+      </c>
       <c r="BJ50">
         <v>9</v>
       </c>
@@ -42295,10 +42112,10 @@
         <v>10</v>
       </c>
       <c r="BG51" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BH51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ51">
         <v>10</v>
@@ -42445,7 +42262,7 @@
         <v>-6</v>
       </c>
       <c r="AT57" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="AX57">
         <v>1</v>
@@ -42531,13 +42348,13 @@
     </row>
     <row r="59" spans="36:68" x14ac:dyDescent="0.45">
       <c r="AJ59" s="3" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="AK59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL59" s="4">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="AX59">
         <v>3</v>
@@ -42583,13 +42400,13 @@
     </row>
     <row r="60" spans="36:68" x14ac:dyDescent="0.45">
       <c r="AJ60" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="AK60">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="AL60" s="4">
-        <v>-7</v>
+        <v>-32</v>
       </c>
       <c r="AX60">
         <v>4</v>
@@ -42631,13 +42448,13 @@
     </row>
     <row r="61" spans="36:68" x14ac:dyDescent="0.45">
       <c r="AJ61" s="3" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="AK61">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="AL61" s="4">
-        <v>-32</v>
+        <v>-17</v>
       </c>
       <c r="AX61">
         <v>5</v>
@@ -42678,15 +42495,6 @@
       <c r="BP61" s="3"/>
     </row>
     <row r="62" spans="36:68" x14ac:dyDescent="0.45">
-      <c r="AJ62" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="AK62">
-        <v>17</v>
-      </c>
-      <c r="AL62" s="4">
-        <v>-17</v>
-      </c>
       <c r="AX62">
         <v>6</v>
       </c>
@@ -42876,7 +42684,9 @@
       <c r="BP66" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="10">
+    <mergeCell ref="AW4:AX4"/>
+    <mergeCell ref="AY4:AZ4"/>
     <mergeCell ref="BA4:BB4"/>
     <mergeCell ref="BC4:BD4"/>
     <mergeCell ref="AK4:AL4"/>
@@ -42885,13 +42695,8 @@
     <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="AS4:AT4"/>
     <mergeCell ref="AU4:AV4"/>
-    <mergeCell ref="AK25:AM25"/>
-    <mergeCell ref="AW4:AX4"/>
-    <mergeCell ref="AY4:AZ4"/>
-    <mergeCell ref="AN25:AQ25"/>
-    <mergeCell ref="AR25:AT25"/>
   </mergeCells>
-  <conditionalFormatting sqref="AJ26:AT42">
+  <conditionalFormatting sqref="AJ26:AT41">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="&quot;-&quot;"/>
@@ -42903,8 +42708,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK27:AT42">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="AK27:AT41">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -42952,89 +42757,89 @@
   <sheetData>
     <row r="1" spans="1:47" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="9"/>
-      <c r="B1" s="20">
-        <v>1</v>
-      </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="20">
-        <v>2</v>
-      </c>
-      <c r="E1" s="21"/>
-      <c r="F1" s="20">
-        <v>3</v>
-      </c>
-      <c r="G1" s="21"/>
-      <c r="H1" s="20">
-        <v>4</v>
-      </c>
-      <c r="I1" s="21"/>
-      <c r="J1" s="20">
+      <c r="B1" s="22">
+        <v>1</v>
+      </c>
+      <c r="C1" s="23"/>
+      <c r="D1" s="22">
+        <v>2</v>
+      </c>
+      <c r="E1" s="23"/>
+      <c r="F1" s="22">
+        <v>3</v>
+      </c>
+      <c r="G1" s="23"/>
+      <c r="H1" s="22">
+        <v>4</v>
+      </c>
+      <c r="I1" s="23"/>
+      <c r="J1" s="22">
         <v>5</v>
       </c>
-      <c r="K1" s="21"/>
-      <c r="L1" s="20">
+      <c r="K1" s="23"/>
+      <c r="L1" s="22">
         <v>6</v>
       </c>
-      <c r="M1" s="21"/>
-      <c r="N1" s="20">
+      <c r="M1" s="23"/>
+      <c r="N1" s="22">
         <v>7</v>
       </c>
-      <c r="O1" s="21"/>
-      <c r="P1" s="20">
+      <c r="O1" s="23"/>
+      <c r="P1" s="22">
         <v>8</v>
       </c>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="20">
+      <c r="Q1" s="23"/>
+      <c r="R1" s="22">
         <v>9</v>
       </c>
-      <c r="S1" s="21"/>
-      <c r="T1" s="20">
+      <c r="S1" s="23"/>
+      <c r="T1" s="22">
         <v>10</v>
       </c>
-      <c r="U1" s="21"/>
+      <c r="U1" s="23"/>
       <c r="Z1" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="AA1" s="20">
-        <v>1</v>
-      </c>
-      <c r="AB1" s="21"/>
-      <c r="AC1" s="20">
-        <v>2</v>
-      </c>
-      <c r="AD1" s="21"/>
-      <c r="AE1" s="20">
-        <v>3</v>
-      </c>
-      <c r="AF1" s="21"/>
-      <c r="AG1" s="20">
-        <v>4</v>
-      </c>
-      <c r="AH1" s="21"/>
-      <c r="AI1" s="20">
+        <v>178</v>
+      </c>
+      <c r="AA1" s="22">
+        <v>1</v>
+      </c>
+      <c r="AB1" s="23"/>
+      <c r="AC1" s="22">
+        <v>2</v>
+      </c>
+      <c r="AD1" s="23"/>
+      <c r="AE1" s="22">
+        <v>3</v>
+      </c>
+      <c r="AF1" s="23"/>
+      <c r="AG1" s="22">
+        <v>4</v>
+      </c>
+      <c r="AH1" s="23"/>
+      <c r="AI1" s="22">
         <v>5</v>
       </c>
-      <c r="AJ1" s="21"/>
-      <c r="AK1" s="20">
+      <c r="AJ1" s="23"/>
+      <c r="AK1" s="22">
         <v>6</v>
       </c>
-      <c r="AL1" s="21"/>
-      <c r="AM1" s="20">
+      <c r="AL1" s="23"/>
+      <c r="AM1" s="22">
         <v>7</v>
       </c>
-      <c r="AN1" s="21"/>
-      <c r="AO1" s="20">
+      <c r="AN1" s="23"/>
+      <c r="AO1" s="22">
         <v>8</v>
       </c>
-      <c r="AP1" s="21"/>
-      <c r="AQ1" s="20">
+      <c r="AP1" s="23"/>
+      <c r="AQ1" s="22">
         <v>9</v>
       </c>
-      <c r="AR1" s="21"/>
-      <c r="AS1" s="20">
+      <c r="AR1" s="23"/>
+      <c r="AS1" s="22">
         <v>10</v>
       </c>
-      <c r="AT1" s="21"/>
+      <c r="AT1" s="23"/>
     </row>
     <row r="2" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="s">
@@ -43206,7 +43011,7 @@
         <v>137</v>
       </c>
       <c r="Z3" s="10" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="AA3" s="17"/>
       <c r="AB3" s="6"/>
@@ -43283,7 +43088,7 @@
         <v>137</v>
       </c>
       <c r="Z4" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AA4" s="17">
         <v>2</v>
@@ -43463,7 +43268,7 @@
         <v>119</v>
       </c>
       <c r="Z6" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="AA6" s="17">
         <v>1</v>
@@ -43565,7 +43370,7 @@
         <v>119</v>
       </c>
       <c r="Z7" s="10" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AA7" s="17"/>
       <c r="AB7" s="6"/>
@@ -43649,7 +43454,7 @@
         <v>119</v>
       </c>
       <c r="Z8" s="10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AA8" s="17">
         <v>3</v>
@@ -43755,7 +43560,7 @@
         <v>119</v>
       </c>
       <c r="Z9" s="10" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="AA9" s="17"/>
       <c r="AB9" s="6"/>
@@ -43831,7 +43636,7 @@
         <v>119</v>
       </c>
       <c r="Z10" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="AA10" s="17">
         <v>2</v>
@@ -43941,7 +43746,7 @@
         <v>119</v>
       </c>
       <c r="Z11" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AA11" s="17">
         <v>4</v>
@@ -44017,7 +43822,7 @@
         <v>119</v>
       </c>
       <c r="Z12" s="10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AA12" s="17">
         <v>2</v>
@@ -44109,7 +43914,7 @@
         <v>119</v>
       </c>
       <c r="Z13" s="10" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AA13" s="17"/>
       <c r="AB13" s="6"/>
@@ -44285,7 +44090,7 @@
         <v>119</v>
       </c>
       <c r="Z15" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AA15" s="17"/>
       <c r="AB15" s="6"/>
@@ -44369,7 +44174,7 @@
         <v>119</v>
       </c>
       <c r="Z16" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AA16" s="17"/>
       <c r="AB16" s="6"/>
@@ -44452,7 +44257,7 @@
         <v>119</v>
       </c>
       <c r="Z17" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AA17" s="17">
         <v>1</v>
@@ -44541,7 +44346,7 @@
         <v>119</v>
       </c>
       <c r="Z18" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AA18" s="17">
         <v>3</v>
@@ -44629,7 +44434,7 @@
         <v>119</v>
       </c>
       <c r="Z19" s="10" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="AA19" s="17"/>
       <c r="AB19" s="6"/>
@@ -44713,7 +44518,7 @@
         <v>119</v>
       </c>
       <c r="Z20" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AA20" s="17"/>
       <c r="AB20" s="6"/>
@@ -44813,7 +44618,7 @@
         <v>119</v>
       </c>
       <c r="Z21" s="10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AA21" s="17">
         <v>1</v>
@@ -44888,7 +44693,7 @@
         <v>119</v>
       </c>
       <c r="Z22" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="AA22" s="17">
         <v>1</v>
@@ -44974,7 +44779,7 @@
         <v>119</v>
       </c>
       <c r="Z23" s="10" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AA23" s="17"/>
       <c r="AB23" s="6"/>
@@ -45142,46 +44947,46 @@
         <v>119</v>
       </c>
       <c r="Z26" s="9"/>
-      <c r="AA26" s="20">
-        <v>1</v>
-      </c>
-      <c r="AB26" s="21"/>
-      <c r="AC26" s="20">
-        <v>2</v>
-      </c>
-      <c r="AD26" s="21"/>
-      <c r="AE26" s="20">
-        <v>3</v>
-      </c>
-      <c r="AF26" s="21"/>
-      <c r="AG26" s="20">
-        <v>4</v>
-      </c>
-      <c r="AH26" s="21"/>
-      <c r="AI26" s="20">
+      <c r="AA26" s="22">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="23"/>
+      <c r="AC26" s="22">
+        <v>2</v>
+      </c>
+      <c r="AD26" s="23"/>
+      <c r="AE26" s="22">
+        <v>3</v>
+      </c>
+      <c r="AF26" s="23"/>
+      <c r="AG26" s="22">
+        <v>4</v>
+      </c>
+      <c r="AH26" s="23"/>
+      <c r="AI26" s="22">
         <v>5</v>
       </c>
-      <c r="AJ26" s="21"/>
-      <c r="AK26" s="20">
+      <c r="AJ26" s="23"/>
+      <c r="AK26" s="22">
         <v>6</v>
       </c>
-      <c r="AL26" s="21"/>
-      <c r="AM26" s="20">
+      <c r="AL26" s="23"/>
+      <c r="AM26" s="22">
         <v>7</v>
       </c>
-      <c r="AN26" s="21"/>
-      <c r="AO26" s="20">
+      <c r="AN26" s="23"/>
+      <c r="AO26" s="22">
         <v>8</v>
       </c>
-      <c r="AP26" s="21"/>
-      <c r="AQ26" s="20">
+      <c r="AP26" s="23"/>
+      <c r="AQ26" s="22">
         <v>9</v>
       </c>
-      <c r="AR26" s="21"/>
-      <c r="AS26" s="20">
+      <c r="AR26" s="23"/>
+      <c r="AS26" s="22">
         <v>10</v>
       </c>
-      <c r="AT26" s="21"/>
+      <c r="AT26" s="23"/>
     </row>
     <row r="27" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A27" s="10" t="s">
@@ -45339,7 +45144,7 @@
         <v>125</v>
       </c>
       <c r="Z28" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="AA28" s="17"/>
       <c r="AB28" s="6"/>
@@ -45415,7 +45220,7 @@
         <v>125</v>
       </c>
       <c r="Z29" s="10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AA29" s="17"/>
       <c r="AB29" s="6"/>
@@ -45479,7 +45284,7 @@
         <v>125</v>
       </c>
       <c r="Z30" s="10" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AA30" s="17"/>
       <c r="AB30" s="6"/>
@@ -45560,7 +45365,7 @@
         <v>125</v>
       </c>
       <c r="Z31" s="10" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AA31" s="17"/>
       <c r="AB31" s="6"/>
@@ -45651,7 +45456,7 @@
         <v>125</v>
       </c>
       <c r="Z32" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AA32" s="17"/>
       <c r="AB32" s="6"/>
@@ -45725,7 +45530,7 @@
         <v>125</v>
       </c>
       <c r="Z33" s="10" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="AA33" s="17"/>
       <c r="AB33" s="6"/>
@@ -45788,7 +45593,7 @@
         <v>125</v>
       </c>
       <c r="Z34" s="10" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AA34" s="17"/>
       <c r="AB34" s="6"/>
@@ -45859,7 +45664,7 @@
         <v>125</v>
       </c>
       <c r="Z35" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AA35" s="17"/>
       <c r="AB35" s="6">
@@ -45940,7 +45745,7 @@
         <v>125</v>
       </c>
       <c r="Z36" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AA36" s="17"/>
       <c r="AB36" s="6"/>
@@ -46003,7 +45808,7 @@
         <v>125</v>
       </c>
       <c r="Z37" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="AA37" s="17"/>
       <c r="AB37" s="6"/>
@@ -46089,7 +45894,7 @@
         <v>125</v>
       </c>
       <c r="Z38" s="10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AA38" s="17"/>
       <c r="AB38" s="6"/>
@@ -46199,46 +46004,46 @@
         <v>138</v>
       </c>
       <c r="Z40" s="9"/>
-      <c r="AA40" s="20">
-        <v>1</v>
-      </c>
-      <c r="AB40" s="21"/>
-      <c r="AC40" s="20">
-        <v>2</v>
-      </c>
-      <c r="AD40" s="21"/>
-      <c r="AE40" s="20">
-        <v>3</v>
-      </c>
-      <c r="AF40" s="21"/>
-      <c r="AG40" s="20">
-        <v>4</v>
-      </c>
-      <c r="AH40" s="21"/>
-      <c r="AI40" s="20">
+      <c r="AA40" s="22">
+        <v>1</v>
+      </c>
+      <c r="AB40" s="23"/>
+      <c r="AC40" s="22">
+        <v>2</v>
+      </c>
+      <c r="AD40" s="23"/>
+      <c r="AE40" s="22">
+        <v>3</v>
+      </c>
+      <c r="AF40" s="23"/>
+      <c r="AG40" s="22">
+        <v>4</v>
+      </c>
+      <c r="AH40" s="23"/>
+      <c r="AI40" s="22">
         <v>5</v>
       </c>
-      <c r="AJ40" s="21"/>
-      <c r="AK40" s="20">
+      <c r="AJ40" s="23"/>
+      <c r="AK40" s="22">
         <v>6</v>
       </c>
-      <c r="AL40" s="21"/>
-      <c r="AM40" s="20">
+      <c r="AL40" s="23"/>
+      <c r="AM40" s="22">
         <v>7</v>
       </c>
-      <c r="AN40" s="21"/>
-      <c r="AO40" s="20">
+      <c r="AN40" s="23"/>
+      <c r="AO40" s="22">
         <v>8</v>
       </c>
-      <c r="AP40" s="21"/>
-      <c r="AQ40" s="20">
+      <c r="AP40" s="23"/>
+      <c r="AQ40" s="22">
         <v>9</v>
       </c>
-      <c r="AR40" s="21"/>
-      <c r="AS40" s="20">
+      <c r="AR40" s="23"/>
+      <c r="AS40" s="22">
         <v>10</v>
       </c>
-      <c r="AT40" s="21"/>
+      <c r="AT40" s="23"/>
     </row>
     <row r="41" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A41" s="10" t="s">
@@ -46401,7 +46206,7 @@
         <v>127</v>
       </c>
       <c r="Z42" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="AA42" s="17"/>
       <c r="AB42" s="6"/>
@@ -46497,7 +46302,7 @@
         <v>129</v>
       </c>
       <c r="Z43" s="10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AA43" s="17"/>
       <c r="AB43" s="6"/>
@@ -46558,7 +46363,7 @@
         <v>155</v>
       </c>
       <c r="Z44" s="10" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AA44" s="17"/>
       <c r="AB44" s="6"/>
@@ -46626,7 +46431,7 @@
         <v>155</v>
       </c>
       <c r="Z45" s="10" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AA45" s="17"/>
       <c r="AB45" s="6"/>
@@ -46700,7 +46505,7 @@
         <v>155</v>
       </c>
       <c r="Z46" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AA46" s="17"/>
       <c r="AB46" s="6"/>
@@ -46761,7 +46566,7 @@
         <v>155</v>
       </c>
       <c r="Z47" s="10" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="AA47" s="17"/>
       <c r="AB47" s="6"/>
@@ -46835,7 +46640,7 @@
         <v>124</v>
       </c>
       <c r="Z48" s="10" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AA48" s="17"/>
       <c r="AB48" s="6"/>
@@ -46865,42 +46670,38 @@
     </row>
     <row r="49" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A49" s="10" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="B49" s="17"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="17">
-        <v>2</v>
-      </c>
+      <c r="C49" s="6">
+        <v>1</v>
+      </c>
+      <c r="D49" s="17"/>
       <c r="E49" s="6"/>
-      <c r="F49" s="17">
-        <v>5</v>
-      </c>
+      <c r="F49" s="17"/>
       <c r="G49" s="6">
-        <v>4</v>
-      </c>
-      <c r="H49" s="17">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H49" s="17"/>
       <c r="I49" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J49" s="17">
         <v>6</v>
       </c>
       <c r="K49" s="6"/>
-      <c r="L49" s="17"/>
+      <c r="L49" s="17">
+        <v>1</v>
+      </c>
       <c r="M49" s="6"/>
-      <c r="N49" s="17">
-        <v>8</v>
-      </c>
+      <c r="N49" s="17"/>
       <c r="O49" s="6"/>
       <c r="P49" s="17"/>
       <c r="Q49" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R49" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S49" s="6"/>
       <c r="T49" s="17">
@@ -46910,10 +46711,10 @@
         <v>1</v>
       </c>
       <c r="V49" s="8" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="Z49" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AA49" s="17"/>
       <c r="AB49" s="6">
@@ -46957,51 +46758,42 @@
     </row>
     <row r="50" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A50" s="10" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="B50" s="17"/>
-      <c r="C50" s="6">
-        <v>1</v>
-      </c>
+      <c r="C50" s="6"/>
       <c r="D50" s="17"/>
       <c r="E50" s="6"/>
-      <c r="F50" s="17"/>
-      <c r="G50" s="6">
-        <v>2</v>
-      </c>
-      <c r="H50" s="17"/>
-      <c r="I50" s="6">
-        <v>1</v>
-      </c>
+      <c r="F50" s="17">
+        <v>1</v>
+      </c>
+      <c r="G50" s="6"/>
+      <c r="H50" s="17">
+        <v>2</v>
+      </c>
+      <c r="I50" s="6"/>
       <c r="J50" s="17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K50" s="6"/>
-      <c r="L50" s="17">
-        <v>1</v>
-      </c>
+      <c r="L50" s="17"/>
       <c r="M50" s="6"/>
       <c r="N50" s="17"/>
       <c r="O50" s="6"/>
-      <c r="P50" s="17"/>
-      <c r="Q50" s="6">
-        <v>2</v>
-      </c>
+      <c r="P50" s="17">
+        <v>2</v>
+      </c>
+      <c r="Q50" s="6"/>
       <c r="R50" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S50" s="6"/>
-      <c r="T50" s="17">
-        <v>6</v>
-      </c>
-      <c r="U50" s="14">
-        <v>1</v>
-      </c>
+      <c r="T50" s="17"/>
       <c r="V50" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Z50" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AA50" s="17"/>
       <c r="AB50" s="6"/>
@@ -47035,42 +46827,36 @@
     </row>
     <row r="51" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A51" s="10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B51" s="17"/>
       <c r="C51" s="6"/>
-      <c r="D51" s="17"/>
+      <c r="D51" s="17">
+        <v>2</v>
+      </c>
       <c r="E51" s="6"/>
       <c r="F51" s="17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G51" s="6"/>
-      <c r="H51" s="17">
-        <v>2</v>
-      </c>
+      <c r="H51" s="17"/>
       <c r="I51" s="6"/>
-      <c r="J51" s="17">
-        <v>4</v>
-      </c>
+      <c r="J51" s="17"/>
       <c r="K51" s="6"/>
       <c r="L51" s="17"/>
       <c r="M51" s="6"/>
       <c r="N51" s="17"/>
       <c r="O51" s="6"/>
-      <c r="P51" s="17">
-        <v>2</v>
-      </c>
+      <c r="P51" s="17"/>
       <c r="Q51" s="6"/>
-      <c r="R51" s="17">
-        <v>2</v>
-      </c>
+      <c r="R51" s="17"/>
       <c r="S51" s="6"/>
       <c r="T51" s="17"/>
       <c r="V51" s="8" t="s">
         <v>122</v>
       </c>
       <c r="Z51" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="AA51" s="17"/>
       <c r="AB51" s="6"/>
@@ -47112,36 +46898,42 @@
     </row>
     <row r="52" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A52" s="10" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B52" s="17"/>
       <c r="C52" s="6"/>
-      <c r="D52" s="17">
-        <v>2</v>
-      </c>
+      <c r="D52" s="17"/>
       <c r="E52" s="6"/>
-      <c r="F52" s="17">
-        <v>4</v>
-      </c>
+      <c r="F52" s="17"/>
       <c r="G52" s="6"/>
-      <c r="H52" s="17"/>
+      <c r="H52" s="17">
+        <v>1</v>
+      </c>
       <c r="I52" s="6"/>
-      <c r="J52" s="17"/>
+      <c r="J52" s="17">
+        <v>2</v>
+      </c>
       <c r="K52" s="6"/>
       <c r="L52" s="17"/>
-      <c r="M52" s="6"/>
+      <c r="M52" s="6">
+        <v>1</v>
+      </c>
       <c r="N52" s="17"/>
       <c r="O52" s="6"/>
-      <c r="P52" s="17"/>
+      <c r="P52" s="17">
+        <v>1</v>
+      </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="17"/>
-      <c r="S52" s="6"/>
+      <c r="S52" s="6">
+        <v>1</v>
+      </c>
       <c r="T52" s="17"/>
       <c r="V52" s="8" t="s">
         <v>122</v>
       </c>
       <c r="Z52" s="10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AA52" s="17"/>
       <c r="AB52" s="6"/>
@@ -47171,97 +46963,89 @@
     </row>
     <row r="53" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A53" s="10" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="B53" s="17"/>
       <c r="C53" s="6"/>
       <c r="D53" s="17"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="17"/>
+      <c r="E53" s="6">
+        <v>1</v>
+      </c>
+      <c r="F53" s="17">
+        <v>1</v>
+      </c>
       <c r="G53" s="6"/>
-      <c r="H53" s="17">
-        <v>1</v>
-      </c>
-      <c r="I53" s="6"/>
+      <c r="H53" s="17"/>
+      <c r="I53" s="6">
+        <v>1</v>
+      </c>
       <c r="J53" s="17">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K53" s="6"/>
       <c r="L53" s="17"/>
       <c r="M53" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N53" s="17"/>
       <c r="O53" s="6"/>
-      <c r="P53" s="17">
-        <v>1</v>
-      </c>
+      <c r="P53" s="17"/>
       <c r="Q53" s="6"/>
       <c r="R53" s="17"/>
       <c r="S53" s="6">
         <v>1</v>
       </c>
-      <c r="T53" s="17"/>
+      <c r="T53" s="17">
+        <v>1</v>
+      </c>
+      <c r="U53" s="14">
+        <v>1</v>
+      </c>
       <c r="V53" s="8" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A54" s="10" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="B54" s="17"/>
       <c r="C54" s="6"/>
       <c r="D54" s="17"/>
-      <c r="E54" s="6">
-        <v>1</v>
-      </c>
+      <c r="E54" s="6"/>
       <c r="F54" s="17">
         <v>1</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="17"/>
-      <c r="I54" s="6">
-        <v>1</v>
-      </c>
-      <c r="J54" s="17">
-        <v>10</v>
-      </c>
+      <c r="I54" s="6"/>
+      <c r="J54" s="17"/>
       <c r="K54" s="6"/>
       <c r="L54" s="17"/>
-      <c r="M54" s="6">
-        <v>3</v>
-      </c>
+      <c r="M54" s="6"/>
       <c r="N54" s="17"/>
       <c r="O54" s="6"/>
       <c r="P54" s="17"/>
       <c r="Q54" s="6"/>
       <c r="R54" s="17"/>
-      <c r="S54" s="6">
-        <v>1</v>
-      </c>
-      <c r="T54" s="17">
-        <v>1</v>
-      </c>
-      <c r="U54" s="14">
-        <v>1</v>
-      </c>
+      <c r="S54" s="6"/>
+      <c r="T54" s="17"/>
       <c r="V54" s="8" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="55" spans="1:47" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A55" s="10" t="s">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="B55" s="17"/>
       <c r="C55" s="6"/>
       <c r="D55" s="17"/>
       <c r="E55" s="6"/>
-      <c r="F55" s="17">
-        <v>1</v>
-      </c>
-      <c r="G55" s="6"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="6">
+        <v>1</v>
+      </c>
       <c r="H55" s="17"/>
       <c r="I55" s="6"/>
       <c r="J55" s="17"/>
@@ -47273,65 +47057,65 @@
       <c r="P55" s="17"/>
       <c r="Q55" s="6"/>
       <c r="R55" s="17"/>
-      <c r="S55" s="6"/>
+      <c r="S55" s="6">
+        <v>1</v>
+      </c>
       <c r="T55" s="17"/>
       <c r="V55" s="8" t="s">
         <v>122</v>
       </c>
       <c r="Z55" s="9"/>
-      <c r="AA55" s="20">
-        <v>1</v>
-      </c>
-      <c r="AB55" s="21"/>
-      <c r="AC55" s="20">
-        <v>2</v>
-      </c>
-      <c r="AD55" s="21"/>
-      <c r="AE55" s="20">
-        <v>3</v>
-      </c>
-      <c r="AF55" s="21"/>
-      <c r="AG55" s="20">
-        <v>4</v>
-      </c>
-      <c r="AH55" s="21"/>
-      <c r="AI55" s="20">
+      <c r="AA55" s="22">
+        <v>1</v>
+      </c>
+      <c r="AB55" s="23"/>
+      <c r="AC55" s="22">
+        <v>2</v>
+      </c>
+      <c r="AD55" s="23"/>
+      <c r="AE55" s="22">
+        <v>3</v>
+      </c>
+      <c r="AF55" s="23"/>
+      <c r="AG55" s="22">
+        <v>4</v>
+      </c>
+      <c r="AH55" s="23"/>
+      <c r="AI55" s="22">
         <v>5</v>
       </c>
-      <c r="AJ55" s="21"/>
-      <c r="AK55" s="20">
+      <c r="AJ55" s="23"/>
+      <c r="AK55" s="22">
         <v>6</v>
       </c>
-      <c r="AL55" s="21"/>
-      <c r="AM55" s="20">
+      <c r="AL55" s="23"/>
+      <c r="AM55" s="22">
         <v>7</v>
       </c>
-      <c r="AN55" s="21"/>
-      <c r="AO55" s="20">
+      <c r="AN55" s="23"/>
+      <c r="AO55" s="22">
         <v>8</v>
       </c>
-      <c r="AP55" s="21"/>
-      <c r="AQ55" s="20">
+      <c r="AP55" s="23"/>
+      <c r="AQ55" s="22">
         <v>9</v>
       </c>
-      <c r="AR55" s="21"/>
-      <c r="AS55" s="20">
+      <c r="AR55" s="23"/>
+      <c r="AS55" s="22">
         <v>10</v>
       </c>
-      <c r="AT55" s="21"/>
+      <c r="AT55" s="23"/>
     </row>
     <row r="56" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A56" s="10" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="B56" s="17"/>
       <c r="C56" s="6"/>
       <c r="D56" s="17"/>
       <c r="E56" s="6"/>
       <c r="F56" s="17"/>
-      <c r="G56" s="6">
-        <v>1</v>
-      </c>
+      <c r="G56" s="6"/>
       <c r="H56" s="17"/>
       <c r="I56" s="6"/>
       <c r="J56" s="17"/>
@@ -47343,10 +47127,11 @@
       <c r="P56" s="17"/>
       <c r="Q56" s="6"/>
       <c r="R56" s="17"/>
-      <c r="S56" s="6">
-        <v>1</v>
-      </c>
+      <c r="S56" s="6"/>
       <c r="T56" s="17"/>
+      <c r="U56" s="14">
+        <v>1</v>
+      </c>
       <c r="V56" s="8" t="s">
         <v>122</v>
       </c>
@@ -47416,29 +47201,42 @@
     </row>
     <row r="57" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A57" s="10" t="s">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="B57" s="17"/>
-      <c r="C57" s="6"/>
+      <c r="C57" s="6">
+        <v>1</v>
+      </c>
       <c r="D57" s="17"/>
       <c r="E57" s="6"/>
-      <c r="F57" s="17"/>
-      <c r="G57" s="6"/>
+      <c r="F57" s="17">
+        <v>1</v>
+      </c>
+      <c r="G57" s="6">
+        <v>3</v>
+      </c>
       <c r="H57" s="17"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="17"/>
+      <c r="I57" s="6">
+        <v>1</v>
+      </c>
+      <c r="J57" s="17">
+        <v>2</v>
+      </c>
       <c r="K57" s="6"/>
-      <c r="L57" s="17"/>
-      <c r="M57" s="6"/>
+      <c r="L57" s="17">
+        <v>1</v>
+      </c>
+      <c r="M57" s="6">
+        <v>1</v>
+      </c>
       <c r="N57" s="17"/>
       <c r="O57" s="6"/>
       <c r="P57" s="17"/>
       <c r="Q57" s="6"/>
       <c r="R57" s="17"/>
       <c r="S57" s="6"/>
-      <c r="T57" s="17"/>
-      <c r="U57" s="14">
-        <v>1</v>
+      <c r="T57" s="17">
+        <v>2</v>
       </c>
       <c r="V57" s="8" t="s">
         <v>122</v>
@@ -47498,34 +47296,24 @@
     </row>
     <row r="58" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A58" s="10" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="B58" s="17"/>
-      <c r="C58" s="6">
-        <v>1</v>
-      </c>
+      <c r="C58" s="6"/>
       <c r="D58" s="17"/>
       <c r="E58" s="6"/>
       <c r="F58" s="17">
         <v>1</v>
       </c>
-      <c r="G58" s="6">
-        <v>3</v>
-      </c>
+      <c r="G58" s="6"/>
       <c r="H58" s="17"/>
-      <c r="I58" s="6">
-        <v>1</v>
-      </c>
+      <c r="I58" s="6"/>
       <c r="J58" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K58" s="6"/>
-      <c r="L58" s="17">
-        <v>1</v>
-      </c>
-      <c r="M58" s="6">
-        <v>1</v>
-      </c>
+      <c r="L58" s="17"/>
+      <c r="M58" s="6"/>
       <c r="N58" s="17"/>
       <c r="O58" s="6"/>
       <c r="P58" s="17"/>
@@ -47533,13 +47321,13 @@
       <c r="R58" s="17"/>
       <c r="S58" s="6"/>
       <c r="T58" s="17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V58" s="8" t="s">
         <v>122</v>
       </c>
       <c r="Z58" s="10" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="AA58" s="17"/>
       <c r="AB58" s="6">
@@ -47591,7 +47379,7 @@
     </row>
     <row r="59" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A59" s="10" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B59" s="17"/>
       <c r="C59" s="6"/>
@@ -47601,28 +47389,36 @@
         <v>1</v>
       </c>
       <c r="G59" s="6"/>
-      <c r="H59" s="17"/>
-      <c r="I59" s="6"/>
+      <c r="H59" s="17">
+        <v>1</v>
+      </c>
+      <c r="I59" s="6">
+        <v>1</v>
+      </c>
       <c r="J59" s="17">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K59" s="6"/>
       <c r="L59" s="17"/>
-      <c r="M59" s="6"/>
+      <c r="M59" s="6">
+        <v>1</v>
+      </c>
       <c r="N59" s="17"/>
       <c r="O59" s="6"/>
-      <c r="P59" s="17"/>
+      <c r="P59" s="17">
+        <v>2</v>
+      </c>
       <c r="Q59" s="6"/>
       <c r="R59" s="17"/>
       <c r="S59" s="6"/>
       <c r="T59" s="17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V59" s="8" t="s">
         <v>122</v>
       </c>
       <c r="Z59" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AA59" s="17"/>
       <c r="AB59" s="6">
@@ -47674,46 +47470,34 @@
     </row>
     <row r="60" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A60" s="10" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="B60" s="17"/>
       <c r="C60" s="6"/>
       <c r="D60" s="17"/>
       <c r="E60" s="6"/>
-      <c r="F60" s="17">
-        <v>1</v>
-      </c>
+      <c r="F60" s="17"/>
       <c r="G60" s="6"/>
-      <c r="H60" s="17">
-        <v>1</v>
-      </c>
-      <c r="I60" s="6">
-        <v>1</v>
-      </c>
-      <c r="J60" s="17">
-        <v>9</v>
-      </c>
+      <c r="H60" s="17"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="17"/>
       <c r="K60" s="6"/>
-      <c r="L60" s="17"/>
-      <c r="M60" s="6">
-        <v>1</v>
-      </c>
+      <c r="L60" s="17">
+        <v>1</v>
+      </c>
+      <c r="M60" s="6"/>
       <c r="N60" s="17"/>
       <c r="O60" s="6"/>
-      <c r="P60" s="17">
-        <v>2</v>
-      </c>
+      <c r="P60" s="17"/>
       <c r="Q60" s="6"/>
       <c r="R60" s="17"/>
       <c r="S60" s="6"/>
-      <c r="T60" s="17">
-        <v>1</v>
-      </c>
+      <c r="T60" s="17"/>
       <c r="V60" s="8" t="s">
         <v>122</v>
       </c>
       <c r="Z60" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AA60" s="17"/>
       <c r="AB60" s="6"/>
@@ -47757,31 +47541,60 @@
     </row>
     <row r="61" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A61" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="B61" s="17"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="17"/>
+        <v>23</v>
+      </c>
+      <c r="B61" s="17">
+        <v>1</v>
+      </c>
+      <c r="C61" s="6">
+        <v>2</v>
+      </c>
+      <c r="D61" s="17">
+        <v>1</v>
+      </c>
       <c r="E61" s="6"/>
-      <c r="F61" s="17"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="17"/>
+      <c r="F61" s="17">
+        <v>1</v>
+      </c>
+      <c r="G61" s="6">
+        <v>2</v>
+      </c>
+      <c r="H61" s="17">
+        <v>2</v>
+      </c>
       <c r="I61" s="6"/>
-      <c r="J61" s="17"/>
-      <c r="K61" s="6"/>
+      <c r="J61" s="17">
+        <v>11</v>
+      </c>
+      <c r="K61" s="6">
+        <v>1</v>
+      </c>
       <c r="L61" s="17">
         <v>1</v>
       </c>
       <c r="M61" s="6"/>
-      <c r="N61" s="17"/>
-      <c r="O61" s="6"/>
-      <c r="P61" s="17"/>
-      <c r="Q61" s="6"/>
+      <c r="N61" s="17">
+        <v>2</v>
+      </c>
+      <c r="O61" s="6">
+        <v>1</v>
+      </c>
+      <c r="P61" s="17">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="6">
+        <v>2</v>
+      </c>
       <c r="R61" s="17"/>
       <c r="S61" s="6"/>
-      <c r="T61" s="17"/>
+      <c r="T61" s="17">
+        <v>1</v>
+      </c>
+      <c r="U61" s="14">
+        <v>3</v>
+      </c>
       <c r="V61" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="Z61" s="10" t="s">
         <v>101</v>
@@ -47816,60 +47629,45 @@
     </row>
     <row r="62" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A62" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B62" s="17">
-        <v>1</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B62" s="17"/>
       <c r="C62" s="6">
-        <v>2</v>
-      </c>
-      <c r="D62" s="17">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D62" s="17"/>
       <c r="E62" s="6"/>
-      <c r="F62" s="17">
-        <v>1</v>
-      </c>
-      <c r="G62" s="6">
-        <v>2</v>
-      </c>
+      <c r="F62" s="17"/>
+      <c r="G62" s="6"/>
       <c r="H62" s="17">
-        <v>2</v>
-      </c>
-      <c r="I62" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="I62" s="6">
+        <v>1</v>
+      </c>
       <c r="J62" s="17">
-        <v>11</v>
-      </c>
-      <c r="K62" s="6">
-        <v>1</v>
-      </c>
-      <c r="L62" s="17">
-        <v>1</v>
-      </c>
-      <c r="M62" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="K62" s="6"/>
+      <c r="L62" s="17"/>
+      <c r="M62" s="6">
+        <v>1</v>
+      </c>
       <c r="N62" s="17">
-        <v>2</v>
-      </c>
-      <c r="O62" s="6">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O62" s="6"/>
       <c r="P62" s="17">
         <v>1</v>
       </c>
-      <c r="Q62" s="6">
-        <v>2</v>
-      </c>
+      <c r="Q62" s="6"/>
       <c r="R62" s="17"/>
       <c r="S62" s="6"/>
       <c r="T62" s="17">
-        <v>1</v>
-      </c>
-      <c r="U62" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V62" s="8" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="Z62" s="10" t="s">
         <v>24</v>
@@ -47922,42 +47720,44 @@
     </row>
     <row r="63" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A63" s="10" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="B63" s="17"/>
-      <c r="C63" s="6">
-        <v>1</v>
-      </c>
+      <c r="C63" s="6"/>
       <c r="D63" s="17"/>
       <c r="E63" s="6"/>
-      <c r="F63" s="17"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="17">
-        <v>1</v>
-      </c>
-      <c r="I63" s="6">
-        <v>1</v>
-      </c>
+      <c r="F63" s="17">
+        <v>1</v>
+      </c>
+      <c r="G63" s="6">
+        <v>1</v>
+      </c>
+      <c r="H63" s="17"/>
+      <c r="I63" s="6"/>
       <c r="J63" s="17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K63" s="6"/>
-      <c r="L63" s="17"/>
+      <c r="L63" s="17">
+        <v>1</v>
+      </c>
       <c r="M63" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N63" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O63" s="6"/>
       <c r="P63" s="17">
         <v>1</v>
       </c>
       <c r="Q63" s="6"/>
-      <c r="R63" s="17"/>
+      <c r="R63" s="17">
+        <v>1</v>
+      </c>
       <c r="S63" s="6"/>
       <c r="T63" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V63" s="8" t="s">
         <v>126</v>
@@ -48013,7 +47813,7 @@
     </row>
     <row r="64" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A64" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B64" s="17"/>
       <c r="C64" s="6"/>
@@ -48022,34 +47822,25 @@
       <c r="F64" s="17">
         <v>1</v>
       </c>
-      <c r="G64" s="6">
-        <v>1</v>
-      </c>
+      <c r="G64" s="6"/>
       <c r="H64" s="17"/>
       <c r="I64" s="6"/>
-      <c r="J64" s="17">
-        <v>5</v>
-      </c>
+      <c r="J64" s="17"/>
       <c r="K64" s="6"/>
-      <c r="L64" s="17">
-        <v>1</v>
-      </c>
-      <c r="M64" s="6">
-        <v>2</v>
-      </c>
-      <c r="N64" s="17">
-        <v>3</v>
-      </c>
+      <c r="L64" s="17"/>
+      <c r="M64" s="6"/>
+      <c r="N64" s="17"/>
       <c r="O64" s="6"/>
-      <c r="P64" s="17">
-        <v>1</v>
-      </c>
+      <c r="P64" s="17"/>
       <c r="Q64" s="6"/>
       <c r="R64" s="17">
         <v>1</v>
       </c>
       <c r="S64" s="6"/>
       <c r="T64" s="17">
+        <v>1</v>
+      </c>
+      <c r="U64" s="14">
         <v>1</v>
       </c>
       <c r="V64" s="8" t="s">
@@ -48100,29 +47891,37 @@
     </row>
     <row r="65" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A65" s="10" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="B65" s="17"/>
       <c r="C65" s="6"/>
       <c r="D65" s="17"/>
       <c r="E65" s="6"/>
       <c r="F65" s="17">
-        <v>1</v>
-      </c>
-      <c r="G65" s="6"/>
-      <c r="H65" s="17"/>
+        <v>2</v>
+      </c>
+      <c r="G65" s="6">
+        <v>2</v>
+      </c>
+      <c r="H65" s="17">
+        <v>1</v>
+      </c>
       <c r="I65" s="6"/>
-      <c r="J65" s="17"/>
+      <c r="J65" s="17">
+        <v>2</v>
+      </c>
       <c r="K65" s="6"/>
-      <c r="L65" s="17"/>
-      <c r="M65" s="6"/>
+      <c r="L65" s="17">
+        <v>1</v>
+      </c>
+      <c r="M65" s="6">
+        <v>1</v>
+      </c>
       <c r="N65" s="17"/>
       <c r="O65" s="6"/>
       <c r="P65" s="17"/>
       <c r="Q65" s="6"/>
-      <c r="R65" s="17">
-        <v>1</v>
-      </c>
+      <c r="R65" s="17"/>
       <c r="S65" s="6"/>
       <c r="T65" s="17">
         <v>1</v>
@@ -48136,213 +47935,212 @@
     </row>
     <row r="66" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A66" s="10" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="B66" s="17"/>
       <c r="C66" s="6"/>
       <c r="D66" s="17"/>
       <c r="E66" s="6"/>
-      <c r="F66" s="17">
-        <v>2</v>
-      </c>
-      <c r="G66" s="6">
-        <v>2</v>
-      </c>
-      <c r="H66" s="17">
-        <v>1</v>
-      </c>
+      <c r="F66" s="17"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="17"/>
       <c r="I66" s="6"/>
-      <c r="J66" s="17">
-        <v>2</v>
-      </c>
+      <c r="J66" s="17"/>
       <c r="K66" s="6"/>
-      <c r="L66" s="17">
-        <v>1</v>
-      </c>
-      <c r="M66" s="6">
-        <v>1</v>
-      </c>
-      <c r="N66" s="17"/>
+      <c r="L66" s="17"/>
+      <c r="M66" s="6"/>
+      <c r="N66" s="17">
+        <v>1</v>
+      </c>
       <c r="O66" s="6"/>
       <c r="P66" s="17"/>
       <c r="Q66" s="6"/>
       <c r="R66" s="17"/>
       <c r="S66" s="6"/>
-      <c r="T66" s="17">
-        <v>1</v>
-      </c>
-      <c r="U66" s="14">
-        <v>1</v>
-      </c>
+      <c r="T66" s="17"/>
       <c r="V66" s="8" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A67" s="10" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="B67" s="17"/>
-      <c r="C67" s="6"/>
+      <c r="C67" s="6">
+        <v>1</v>
+      </c>
       <c r="D67" s="17"/>
       <c r="E67" s="6"/>
-      <c r="F67" s="17"/>
-      <c r="G67" s="6"/>
+      <c r="F67" s="17">
+        <v>1</v>
+      </c>
+      <c r="G67" s="6">
+        <v>1</v>
+      </c>
       <c r="H67" s="17"/>
       <c r="I67" s="6"/>
-      <c r="J67" s="17"/>
-      <c r="K67" s="6"/>
-      <c r="L67" s="17"/>
+      <c r="J67" s="17">
+        <v>2</v>
+      </c>
+      <c r="K67" s="6">
+        <v>1</v>
+      </c>
+      <c r="L67" s="17">
+        <v>1</v>
+      </c>
       <c r="M67" s="6"/>
-      <c r="N67" s="17">
-        <v>1</v>
-      </c>
+      <c r="N67" s="17"/>
       <c r="O67" s="6"/>
-      <c r="P67" s="17"/>
+      <c r="P67" s="17">
+        <v>1</v>
+      </c>
       <c r="Q67" s="6"/>
-      <c r="R67" s="17"/>
+      <c r="R67" s="17">
+        <v>1</v>
+      </c>
       <c r="S67" s="6"/>
-      <c r="T67" s="17"/>
+      <c r="T67" s="17">
+        <v>2</v>
+      </c>
+      <c r="U67" s="14">
+        <v>2</v>
+      </c>
       <c r="V67" s="8" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="68" spans="1:47" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A68" s="10" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B68" s="17"/>
       <c r="C68" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D68" s="17"/>
-      <c r="E68" s="6"/>
+      <c r="E68" s="6">
+        <v>1</v>
+      </c>
       <c r="F68" s="17">
-        <v>1</v>
-      </c>
-      <c r="G68" s="6">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G68" s="6"/>
       <c r="H68" s="17"/>
       <c r="I68" s="6"/>
       <c r="J68" s="17">
-        <v>2</v>
-      </c>
-      <c r="K68" s="6">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K68" s="6"/>
       <c r="L68" s="17">
         <v>1</v>
       </c>
-      <c r="M68" s="6"/>
-      <c r="N68" s="17"/>
+      <c r="M68" s="6">
+        <v>2</v>
+      </c>
+      <c r="N68" s="17">
+        <v>1</v>
+      </c>
       <c r="O68" s="6"/>
       <c r="P68" s="17">
-        <v>1</v>
-      </c>
-      <c r="Q68" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="Q68" s="6">
+        <v>1</v>
+      </c>
       <c r="R68" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S68" s="6"/>
       <c r="T68" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U68" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V68" s="8" t="s">
         <v>126</v>
       </c>
       <c r="Z68" s="9"/>
-      <c r="AA68" s="20">
-        <v>1</v>
-      </c>
-      <c r="AB68" s="21"/>
-      <c r="AC68" s="20">
-        <v>2</v>
-      </c>
-      <c r="AD68" s="21"/>
-      <c r="AE68" s="20">
-        <v>3</v>
-      </c>
-      <c r="AF68" s="21"/>
-      <c r="AG68" s="20">
-        <v>4</v>
-      </c>
-      <c r="AH68" s="21"/>
-      <c r="AI68" s="20">
+      <c r="AA68" s="22">
+        <v>1</v>
+      </c>
+      <c r="AB68" s="23"/>
+      <c r="AC68" s="22">
+        <v>2</v>
+      </c>
+      <c r="AD68" s="23"/>
+      <c r="AE68" s="22">
+        <v>3</v>
+      </c>
+      <c r="AF68" s="23"/>
+      <c r="AG68" s="22">
+        <v>4</v>
+      </c>
+      <c r="AH68" s="23"/>
+      <c r="AI68" s="22">
         <v>5</v>
       </c>
-      <c r="AJ68" s="21"/>
-      <c r="AK68" s="20">
+      <c r="AJ68" s="23"/>
+      <c r="AK68" s="22">
         <v>6</v>
       </c>
-      <c r="AL68" s="21"/>
-      <c r="AM68" s="20">
+      <c r="AL68" s="23"/>
+      <c r="AM68" s="22">
         <v>7</v>
       </c>
-      <c r="AN68" s="21"/>
-      <c r="AO68" s="20">
+      <c r="AN68" s="23"/>
+      <c r="AO68" s="22">
         <v>8</v>
       </c>
-      <c r="AP68" s="21"/>
-      <c r="AQ68" s="20">
+      <c r="AP68" s="23"/>
+      <c r="AQ68" s="22">
         <v>9</v>
       </c>
-      <c r="AR68" s="21"/>
-      <c r="AS68" s="20">
+      <c r="AR68" s="23"/>
+      <c r="AS68" s="22">
         <v>10</v>
       </c>
-      <c r="AT68" s="21"/>
+      <c r="AT68" s="23"/>
     </row>
     <row r="69" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A69" s="10" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="B69" s="17"/>
-      <c r="C69" s="6">
-        <v>4</v>
-      </c>
-      <c r="D69" s="17"/>
-      <c r="E69" s="6">
-        <v>1</v>
-      </c>
+      <c r="C69" s="6"/>
+      <c r="D69" s="17">
+        <v>1</v>
+      </c>
+      <c r="E69" s="6"/>
       <c r="F69" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G69" s="6"/>
       <c r="H69" s="17"/>
       <c r="I69" s="6"/>
       <c r="J69" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K69" s="6"/>
-      <c r="L69" s="17">
-        <v>1</v>
-      </c>
-      <c r="M69" s="6">
-        <v>2</v>
-      </c>
+      <c r="L69" s="17"/>
+      <c r="M69" s="6"/>
       <c r="N69" s="17">
-        <v>1</v>
-      </c>
-      <c r="O69" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="O69" s="6">
+        <v>1</v>
+      </c>
       <c r="P69" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q69" s="6">
         <v>1</v>
       </c>
-      <c r="R69" s="17">
-        <v>3</v>
-      </c>
+      <c r="R69" s="17"/>
       <c r="S69" s="6"/>
       <c r="T69" s="17">
-        <v>1</v>
-      </c>
-      <c r="U69" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V69" s="8" t="s">
         <v>126</v>
@@ -48413,48 +48211,49 @@
     </row>
     <row r="70" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A70" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70" s="17"/>
+        <v>51</v>
+      </c>
+      <c r="B70" s="17">
+        <v>1</v>
+      </c>
       <c r="C70" s="6"/>
-      <c r="D70" s="17">
-        <v>1</v>
-      </c>
+      <c r="D70" s="17"/>
       <c r="E70" s="6"/>
       <c r="F70" s="17">
-        <v>1</v>
-      </c>
-      <c r="G70" s="6"/>
-      <c r="H70" s="17"/>
+        <v>2</v>
+      </c>
+      <c r="G70" s="6">
+        <v>1</v>
+      </c>
+      <c r="H70" s="17">
+        <v>1</v>
+      </c>
       <c r="I70" s="6"/>
-      <c r="J70" s="17">
-        <v>1</v>
-      </c>
-      <c r="K70" s="6"/>
+      <c r="J70" s="17"/>
+      <c r="K70" s="6">
+        <v>1</v>
+      </c>
       <c r="L70" s="17"/>
       <c r="M70" s="6"/>
-      <c r="N70" s="17">
-        <v>2</v>
-      </c>
+      <c r="N70" s="17"/>
       <c r="O70" s="6">
         <v>1</v>
       </c>
-      <c r="P70" s="17">
-        <v>1</v>
-      </c>
-      <c r="Q70" s="6">
-        <v>1</v>
-      </c>
+      <c r="P70" s="17"/>
+      <c r="Q70" s="6"/>
       <c r="R70" s="17"/>
       <c r="S70" s="6"/>
       <c r="T70" s="17">
         <v>2</v>
       </c>
+      <c r="U70" s="14">
+        <v>2</v>
+      </c>
       <c r="V70" s="8" t="s">
         <v>126</v>
       </c>
       <c r="Z70" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB70">
         <v>1</v>
@@ -48492,49 +48291,47 @@
     </row>
     <row r="71" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A71" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="B71" s="17">
-        <v>1</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="B71" s="17"/>
       <c r="C71" s="6"/>
       <c r="D71" s="17"/>
       <c r="E71" s="6"/>
-      <c r="F71" s="17">
-        <v>2</v>
-      </c>
-      <c r="G71" s="6">
-        <v>1</v>
-      </c>
-      <c r="H71" s="17">
-        <v>1</v>
-      </c>
+      <c r="F71" s="17"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="17"/>
       <c r="I71" s="6"/>
-      <c r="J71" s="17"/>
-      <c r="K71" s="6">
-        <v>1</v>
-      </c>
+      <c r="J71" s="17">
+        <v>4</v>
+      </c>
+      <c r="K71" s="6"/>
       <c r="L71" s="17"/>
-      <c r="M71" s="6"/>
-      <c r="N71" s="17"/>
-      <c r="O71" s="6">
-        <v>1</v>
-      </c>
+      <c r="M71" s="6">
+        <v>2</v>
+      </c>
+      <c r="N71" s="17">
+        <v>2</v>
+      </c>
+      <c r="O71" s="6"/>
       <c r="P71" s="17"/>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="17"/>
+      <c r="Q71" s="6">
+        <v>1</v>
+      </c>
+      <c r="R71" s="17">
+        <v>1</v>
+      </c>
       <c r="S71" s="6"/>
       <c r="T71" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U71" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V71" s="8" t="s">
         <v>126</v>
       </c>
       <c r="Z71" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AC71">
         <v>1</v>
@@ -48569,47 +48366,57 @@
     </row>
     <row r="72" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A72" s="10" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="B72" s="17"/>
       <c r="C72" s="6"/>
-      <c r="D72" s="17"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="17"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="17"/>
+      <c r="D72" s="17">
+        <v>1</v>
+      </c>
+      <c r="E72" s="6">
+        <v>2</v>
+      </c>
+      <c r="F72" s="17">
+        <v>3</v>
+      </c>
+      <c r="G72" s="6">
+        <v>1</v>
+      </c>
+      <c r="H72" s="17">
+        <v>2</v>
+      </c>
       <c r="I72" s="6"/>
       <c r="J72" s="17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K72" s="6"/>
-      <c r="L72" s="17"/>
+      <c r="L72" s="17">
+        <v>2</v>
+      </c>
       <c r="M72" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N72" s="17">
-        <v>2</v>
-      </c>
-      <c r="O72" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="O72" s="6">
+        <v>1</v>
+      </c>
       <c r="P72" s="17"/>
-      <c r="Q72" s="6">
-        <v>1</v>
-      </c>
-      <c r="R72" s="17">
-        <v>1</v>
-      </c>
+      <c r="Q72" s="6"/>
+      <c r="R72" s="17"/>
       <c r="S72" s="6"/>
       <c r="T72" s="17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U72" s="14">
         <v>1</v>
       </c>
       <c r="V72" s="8" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="Z72" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AA72">
         <v>1</v>
@@ -48635,48 +48442,56 @@
     </row>
     <row r="73" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A73" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B73" s="17"/>
-      <c r="C73" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="B73" s="17">
+        <v>1</v>
+      </c>
+      <c r="C73" s="6">
+        <v>1</v>
+      </c>
       <c r="D73" s="17">
         <v>1</v>
       </c>
-      <c r="E73" s="6">
-        <v>2</v>
-      </c>
+      <c r="E73" s="6"/>
       <c r="F73" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G73" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H73" s="17">
-        <v>2</v>
-      </c>
-      <c r="I73" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="I73" s="6">
+        <v>2</v>
+      </c>
       <c r="J73" s="17">
-        <v>7</v>
-      </c>
-      <c r="K73" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="K73" s="6">
+        <v>1</v>
+      </c>
       <c r="L73" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M73" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N73" s="17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O73" s="6">
         <v>1</v>
       </c>
       <c r="P73" s="17"/>
-      <c r="Q73" s="6"/>
+      <c r="Q73" s="6">
+        <v>1</v>
+      </c>
       <c r="R73" s="17"/>
       <c r="S73" s="6"/>
       <c r="T73" s="17">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U73" s="14">
         <v>1</v>
@@ -48685,7 +48500,7 @@
         <v>132</v>
       </c>
       <c r="Z73" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AI73">
         <v>1</v>
@@ -48702,65 +48517,59 @@
     </row>
     <row r="74" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A74" s="10" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="B74" s="17">
         <v>1</v>
       </c>
-      <c r="C74" s="6">
-        <v>1</v>
-      </c>
-      <c r="D74" s="17">
-        <v>1</v>
-      </c>
+      <c r="C74" s="6"/>
+      <c r="D74" s="17"/>
       <c r="E74" s="6"/>
       <c r="F74" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G74" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H74" s="17">
-        <v>1</v>
-      </c>
-      <c r="I74" s="6">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I74" s="6"/>
       <c r="J74" s="17">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K74" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L74" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M74" s="6">
         <v>3</v>
       </c>
       <c r="N74" s="17">
-        <v>4</v>
-      </c>
-      <c r="O74" s="6">
-        <v>1</v>
-      </c>
-      <c r="P74" s="17"/>
+        <v>7</v>
+      </c>
+      <c r="O74" s="6"/>
+      <c r="P74" s="17">
+        <v>2</v>
+      </c>
       <c r="Q74" s="6">
         <v>1</v>
       </c>
       <c r="R74" s="17"/>
       <c r="S74" s="6"/>
       <c r="T74" s="17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U74" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V74" s="8" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="Z74" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AB74">
         <v>1</v>
@@ -48795,59 +48604,57 @@
     </row>
     <row r="75" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A75" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="B75" s="17">
-        <v>1</v>
-      </c>
-      <c r="C75" s="6"/>
+        <v>19</v>
+      </c>
+      <c r="B75" s="17"/>
+      <c r="C75" s="6">
+        <v>2</v>
+      </c>
       <c r="D75" s="17"/>
       <c r="E75" s="6"/>
       <c r="F75" s="17">
-        <v>5</v>
-      </c>
-      <c r="G75" s="6">
-        <v>1</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="G75" s="6"/>
       <c r="H75" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I75" s="6"/>
       <c r="J75" s="17">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K75" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L75" s="17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M75" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N75" s="17">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O75" s="6"/>
       <c r="P75" s="17">
         <v>2</v>
       </c>
       <c r="Q75" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R75" s="17"/>
       <c r="S75" s="6"/>
       <c r="T75" s="17">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U75" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V75" s="8" t="s">
         <v>135</v>
       </c>
       <c r="Z75" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AA75">
         <v>1</v>
@@ -48888,7 +48695,7 @@
     </row>
     <row r="76" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A76" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B76" s="17"/>
       <c r="C76" s="6">
@@ -48897,7 +48704,7 @@
       <c r="D76" s="17"/>
       <c r="E76" s="6"/>
       <c r="F76" s="17">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G76" s="6"/>
       <c r="H76" s="17">
@@ -48910,26 +48717,26 @@
       <c r="K76" s="6">
         <v>1</v>
       </c>
-      <c r="L76" s="17">
-        <v>1</v>
-      </c>
+      <c r="L76" s="17"/>
       <c r="M76" s="6">
         <v>1</v>
       </c>
       <c r="N76" s="17">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O76" s="6"/>
       <c r="P76" s="17">
         <v>2</v>
       </c>
       <c r="Q76" s="6">
-        <v>2</v>
-      </c>
-      <c r="R76" s="17"/>
+        <v>3</v>
+      </c>
+      <c r="R76" s="17">
+        <v>1</v>
+      </c>
       <c r="S76" s="6"/>
       <c r="T76" s="17">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U76" s="14">
         <v>1</v>
@@ -48938,7 +48745,7 @@
         <v>135</v>
       </c>
       <c r="Z76" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AE76">
         <v>2</v>
@@ -48973,57 +48780,48 @@
     </row>
     <row r="77" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A77" s="10" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="B77" s="17"/>
-      <c r="C77" s="6">
-        <v>2</v>
-      </c>
+      <c r="C77" s="6"/>
       <c r="D77" s="17"/>
       <c r="E77" s="6"/>
       <c r="F77" s="17">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G77" s="6"/>
       <c r="H77" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I77" s="6"/>
       <c r="J77" s="17">
-        <v>3</v>
-      </c>
-      <c r="K77" s="6">
-        <v>1</v>
-      </c>
-      <c r="L77" s="17"/>
-      <c r="M77" s="6">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K77" s="6"/>
+      <c r="L77" s="17">
+        <v>2</v>
+      </c>
+      <c r="M77" s="6"/>
       <c r="N77" s="17">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O77" s="6"/>
       <c r="P77" s="17">
         <v>2</v>
       </c>
       <c r="Q77" s="6">
-        <v>3</v>
-      </c>
-      <c r="R77" s="17">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="R77" s="17"/>
       <c r="S77" s="6"/>
       <c r="T77" s="17">
-        <v>4</v>
-      </c>
-      <c r="U77" s="14">
         <v>1</v>
       </c>
       <c r="V77" s="8" t="s">
         <v>135</v>
       </c>
       <c r="Z77" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AF77">
         <v>1</v>
@@ -49040,48 +48838,36 @@
     </row>
     <row r="78" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A78" s="10" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="B78" s="17"/>
       <c r="C78" s="6"/>
       <c r="D78" s="17"/>
       <c r="E78" s="6"/>
       <c r="F78" s="17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G78" s="6"/>
-      <c r="H78" s="17">
-        <v>1</v>
-      </c>
+      <c r="H78" s="17"/>
       <c r="I78" s="6"/>
-      <c r="J78" s="17">
-        <v>2</v>
-      </c>
+      <c r="J78" s="17"/>
       <c r="K78" s="6"/>
-      <c r="L78" s="17">
-        <v>2</v>
-      </c>
+      <c r="L78" s="17"/>
       <c r="M78" s="6"/>
-      <c r="N78" s="17">
-        <v>2</v>
-      </c>
+      <c r="N78" s="17"/>
       <c r="O78" s="6"/>
-      <c r="P78" s="17">
-        <v>2</v>
-      </c>
+      <c r="P78" s="17"/>
       <c r="Q78" s="6">
         <v>2</v>
       </c>
       <c r="R78" s="17"/>
       <c r="S78" s="6"/>
-      <c r="T78" s="17">
-        <v>1</v>
-      </c>
+      <c r="T78" s="17"/>
       <c r="V78" s="8" t="s">
         <v>135</v>
       </c>
       <c r="Z78" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AB78">
         <v>1</v>
@@ -49113,36 +48899,54 @@
     </row>
     <row r="79" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A79" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B79" s="17"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="17"/>
+        <v>24</v>
+      </c>
+      <c r="B79" s="17">
+        <v>1</v>
+      </c>
+      <c r="C79" s="6">
+        <v>1</v>
+      </c>
+      <c r="D79" s="17">
+        <v>1</v>
+      </c>
       <c r="E79" s="6"/>
       <c r="F79" s="17">
-        <v>2</v>
-      </c>
-      <c r="G79" s="6"/>
-      <c r="H79" s="17"/>
+        <v>7</v>
+      </c>
+      <c r="G79" s="6">
+        <v>4</v>
+      </c>
+      <c r="H79" s="17">
+        <v>2</v>
+      </c>
       <c r="I79" s="6"/>
-      <c r="J79" s="17"/>
+      <c r="J79" s="17">
+        <v>7</v>
+      </c>
       <c r="K79" s="6"/>
       <c r="L79" s="17"/>
       <c r="M79" s="6"/>
-      <c r="N79" s="17"/>
+      <c r="N79" s="17">
+        <v>5</v>
+      </c>
       <c r="O79" s="6"/>
-      <c r="P79" s="17"/>
+      <c r="P79" s="17">
+        <v>1</v>
+      </c>
       <c r="Q79" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R79" s="17"/>
       <c r="S79" s="6"/>
-      <c r="T79" s="17"/>
+      <c r="T79" s="17">
+        <v>1</v>
+      </c>
       <c r="V79" s="8" t="s">
         <v>135</v>
       </c>
       <c r="Z79" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AE79">
         <v>2</v>
@@ -49168,54 +48972,54 @@
     </row>
     <row r="80" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A80" s="10" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="B80" s="17">
         <v>1</v>
       </c>
-      <c r="C80" s="6">
-        <v>1</v>
-      </c>
-      <c r="D80" s="17">
-        <v>1</v>
-      </c>
+      <c r="C80" s="6"/>
+      <c r="D80" s="17"/>
       <c r="E80" s="6"/>
       <c r="F80" s="17">
-        <v>7</v>
-      </c>
-      <c r="G80" s="6">
-        <v>4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G80" s="6"/>
       <c r="H80" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I80" s="6"/>
       <c r="J80" s="17">
-        <v>7</v>
-      </c>
-      <c r="K80" s="6"/>
-      <c r="L80" s="17"/>
-      <c r="M80" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="K80" s="6">
+        <v>2</v>
+      </c>
+      <c r="L80" s="17">
+        <v>5</v>
+      </c>
+      <c r="M80" s="6">
+        <v>2</v>
+      </c>
       <c r="N80" s="17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O80" s="6"/>
       <c r="P80" s="17">
         <v>1</v>
       </c>
       <c r="Q80" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R80" s="17"/>
       <c r="S80" s="6"/>
       <c r="T80" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V80" s="8" t="s">
         <v>135</v>
       </c>
       <c r="Z80" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AI80">
         <v>3</v>
@@ -49229,54 +49033,48 @@
     </row>
     <row r="81" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A81" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="B81" s="17">
-        <v>1</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B81" s="17"/>
       <c r="C81" s="6"/>
-      <c r="D81" s="17"/>
+      <c r="D81" s="17">
+        <v>1</v>
+      </c>
       <c r="E81" s="6"/>
       <c r="F81" s="17">
-        <v>5</v>
-      </c>
-      <c r="G81" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="G81" s="6">
+        <v>2</v>
+      </c>
       <c r="H81" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I81" s="6"/>
       <c r="J81" s="17">
         <v>6</v>
       </c>
-      <c r="K81" s="6">
-        <v>2</v>
-      </c>
-      <c r="L81" s="17">
-        <v>5</v>
-      </c>
+      <c r="K81" s="6"/>
+      <c r="L81" s="17"/>
       <c r="M81" s="6">
         <v>2</v>
       </c>
-      <c r="N81" s="17">
-        <v>4</v>
-      </c>
+      <c r="N81" s="17"/>
       <c r="O81" s="6"/>
-      <c r="P81" s="17">
-        <v>1</v>
-      </c>
+      <c r="P81" s="17"/>
       <c r="Q81" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R81" s="17"/>
-      <c r="S81" s="6"/>
-      <c r="T81" s="17">
-        <v>3</v>
-      </c>
+      <c r="S81" s="6">
+        <v>1</v>
+      </c>
+      <c r="T81" s="17"/>
       <c r="V81" s="8" t="s">
         <v>135</v>
       </c>
       <c r="Z81" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AA81">
         <v>1</v>
@@ -49311,62 +49109,54 @@
     </row>
     <row r="82" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A82" s="10" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="B82" s="17"/>
       <c r="C82" s="6"/>
-      <c r="D82" s="17">
-        <v>1</v>
-      </c>
+      <c r="D82" s="17"/>
       <c r="E82" s="6"/>
-      <c r="F82" s="17">
-        <v>2</v>
-      </c>
-      <c r="G82" s="6">
-        <v>2</v>
-      </c>
-      <c r="H82" s="17">
-        <v>2</v>
-      </c>
+      <c r="F82" s="17"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="17"/>
       <c r="I82" s="6"/>
-      <c r="J82" s="17">
-        <v>6</v>
-      </c>
+      <c r="J82" s="17"/>
       <c r="K82" s="6"/>
       <c r="L82" s="17"/>
-      <c r="M82" s="6">
-        <v>2</v>
-      </c>
+      <c r="M82" s="6"/>
       <c r="N82" s="17"/>
       <c r="O82" s="6"/>
       <c r="P82" s="17"/>
-      <c r="Q82" s="6">
-        <v>1</v>
-      </c>
+      <c r="Q82" s="6"/>
       <c r="R82" s="17"/>
-      <c r="S82" s="6">
-        <v>1</v>
-      </c>
-      <c r="T82" s="17"/>
+      <c r="S82" s="6"/>
+      <c r="T82" s="17">
+        <v>1</v>
+      </c>
       <c r="V82" s="8" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
     </row>
     <row r="83" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A83" s="10" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="B83" s="17"/>
       <c r="C83" s="6"/>
       <c r="D83" s="17"/>
       <c r="E83" s="6"/>
-      <c r="F83" s="17"/>
+      <c r="F83" s="17">
+        <v>1</v>
+      </c>
       <c r="G83" s="6"/>
       <c r="H83" s="17"/>
       <c r="I83" s="6"/>
-      <c r="J83" s="17"/>
+      <c r="J83" s="17">
+        <v>4</v>
+      </c>
       <c r="K83" s="6"/>
-      <c r="L83" s="17"/>
+      <c r="L83" s="17">
+        <v>1</v>
+      </c>
       <c r="M83" s="6"/>
       <c r="N83" s="17"/>
       <c r="O83" s="6"/>
@@ -49383,102 +49173,104 @@
     </row>
     <row r="84" spans="1:47" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A84" s="10" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="B84" s="17"/>
       <c r="C84" s="6"/>
       <c r="D84" s="17"/>
       <c r="E84" s="6"/>
-      <c r="F84" s="17">
-        <v>1</v>
-      </c>
+      <c r="F84" s="17"/>
       <c r="G84" s="6"/>
       <c r="H84" s="17"/>
       <c r="I84" s="6"/>
-      <c r="J84" s="17">
-        <v>4</v>
-      </c>
+      <c r="J84" s="17"/>
       <c r="K84" s="6"/>
-      <c r="L84" s="17">
-        <v>1</v>
-      </c>
+      <c r="L84" s="17"/>
       <c r="M84" s="6"/>
       <c r="N84" s="17"/>
       <c r="O84" s="6"/>
       <c r="P84" s="17"/>
-      <c r="Q84" s="6"/>
+      <c r="Q84" s="6">
+        <v>2</v>
+      </c>
       <c r="R84" s="17"/>
       <c r="S84" s="6"/>
-      <c r="T84" s="17">
-        <v>1</v>
-      </c>
+      <c r="T84" s="17"/>
       <c r="V84" s="8" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="Z84" s="9"/>
-      <c r="AA84" s="20">
-        <v>1</v>
-      </c>
-      <c r="AB84" s="21"/>
-      <c r="AC84" s="20">
-        <v>2</v>
-      </c>
-      <c r="AD84" s="21"/>
-      <c r="AE84" s="20">
-        <v>3</v>
-      </c>
-      <c r="AF84" s="21"/>
-      <c r="AG84" s="20">
-        <v>4</v>
-      </c>
-      <c r="AH84" s="21"/>
-      <c r="AI84" s="20">
+      <c r="AA84" s="22">
+        <v>1</v>
+      </c>
+      <c r="AB84" s="23"/>
+      <c r="AC84" s="22">
+        <v>2</v>
+      </c>
+      <c r="AD84" s="23"/>
+      <c r="AE84" s="22">
+        <v>3</v>
+      </c>
+      <c r="AF84" s="23"/>
+      <c r="AG84" s="22">
+        <v>4</v>
+      </c>
+      <c r="AH84" s="23"/>
+      <c r="AI84" s="22">
         <v>5</v>
       </c>
-      <c r="AJ84" s="21"/>
-      <c r="AK84" s="20">
+      <c r="AJ84" s="23"/>
+      <c r="AK84" s="22">
         <v>6</v>
       </c>
-      <c r="AL84" s="21"/>
-      <c r="AM84" s="20">
+      <c r="AL84" s="23"/>
+      <c r="AM84" s="22">
         <v>7</v>
       </c>
-      <c r="AN84" s="21"/>
-      <c r="AO84" s="20">
+      <c r="AN84" s="23"/>
+      <c r="AO84" s="22">
         <v>8</v>
       </c>
-      <c r="AP84" s="21"/>
-      <c r="AQ84" s="20">
+      <c r="AP84" s="23"/>
+      <c r="AQ84" s="22">
         <v>9</v>
       </c>
-      <c r="AR84" s="21"/>
-      <c r="AS84" s="20">
+      <c r="AR84" s="23"/>
+      <c r="AS84" s="22">
         <v>10</v>
       </c>
-      <c r="AT84" s="21"/>
+      <c r="AT84" s="23"/>
     </row>
     <row r="85" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A85" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="B85" s="17"/>
+        <v>42</v>
+      </c>
+      <c r="B85" s="17">
+        <v>1</v>
+      </c>
       <c r="C85" s="6"/>
-      <c r="D85" s="17"/>
+      <c r="D85" s="17">
+        <v>2</v>
+      </c>
       <c r="E85" s="6"/>
-      <c r="F85" s="17"/>
+      <c r="F85" s="17">
+        <v>4</v>
+      </c>
       <c r="G85" s="6"/>
       <c r="H85" s="17"/>
       <c r="I85" s="6"/>
-      <c r="J85" s="17"/>
+      <c r="J85" s="17">
+        <v>8</v>
+      </c>
       <c r="K85" s="6"/>
       <c r="L85" s="17"/>
-      <c r="M85" s="6"/>
+      <c r="M85" s="6">
+        <v>2</v>
+      </c>
       <c r="N85" s="17"/>
       <c r="O85" s="6"/>
       <c r="P85" s="17"/>
-      <c r="Q85" s="6">
-        <v>2</v>
-      </c>
+      <c r="Q85" s="6"/>
       <c r="R85" s="17"/>
       <c r="S85" s="6"/>
       <c r="T85" s="17"/>
@@ -49551,37 +49343,31 @@
     </row>
     <row r="86" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A86" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B86" s="17">
-        <v>1</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="B86" s="17"/>
       <c r="C86" s="6"/>
-      <c r="D86" s="17">
-        <v>2</v>
-      </c>
+      <c r="D86" s="17"/>
       <c r="E86" s="6"/>
-      <c r="F86" s="17">
-        <v>4</v>
-      </c>
+      <c r="F86" s="17"/>
       <c r="G86" s="6"/>
       <c r="H86" s="17"/>
       <c r="I86" s="6"/>
       <c r="J86" s="17">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K86" s="6"/>
       <c r="L86" s="17"/>
-      <c r="M86" s="6">
-        <v>2</v>
-      </c>
+      <c r="M86" s="6"/>
       <c r="N86" s="17"/>
       <c r="O86" s="6"/>
       <c r="P86" s="17"/>
       <c r="Q86" s="6"/>
       <c r="R86" s="17"/>
       <c r="S86" s="6"/>
-      <c r="T86" s="17"/>
+      <c r="T86" s="17">
+        <v>1</v>
+      </c>
       <c r="V86" s="8" t="s">
         <v>136</v>
       </c>
@@ -49626,10 +49412,12 @@
     </row>
     <row r="87" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A87" s="10" t="s">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="B87" s="17"/>
-      <c r="C87" s="6"/>
+      <c r="C87" s="6">
+        <v>1</v>
+      </c>
       <c r="D87" s="17"/>
       <c r="E87" s="6"/>
       <c r="F87" s="17"/>
@@ -49637,12 +49425,14 @@
       <c r="H87" s="17"/>
       <c r="I87" s="6"/>
       <c r="J87" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K87" s="6"/>
       <c r="L87" s="17"/>
       <c r="M87" s="6"/>
-      <c r="N87" s="17"/>
+      <c r="N87" s="17">
+        <v>1</v>
+      </c>
       <c r="O87" s="6"/>
       <c r="P87" s="17"/>
       <c r="Q87" s="6"/>
@@ -49695,35 +49485,35 @@
     </row>
     <row r="88" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A88" s="10" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="B88" s="17"/>
-      <c r="C88" s="6">
-        <v>1</v>
-      </c>
+      <c r="C88" s="6"/>
       <c r="D88" s="17"/>
       <c r="E88" s="6"/>
-      <c r="F88" s="17"/>
+      <c r="F88" s="17">
+        <v>1</v>
+      </c>
       <c r="G88" s="6"/>
       <c r="H88" s="17"/>
-      <c r="I88" s="6"/>
+      <c r="I88" s="6">
+        <v>1</v>
+      </c>
       <c r="J88" s="17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K88" s="6"/>
       <c r="L88" s="17"/>
-      <c r="M88" s="6"/>
-      <c r="N88" s="17">
-        <v>1</v>
-      </c>
+      <c r="M88" s="6">
+        <v>1</v>
+      </c>
+      <c r="N88" s="17"/>
       <c r="O88" s="6"/>
       <c r="P88" s="17"/>
       <c r="Q88" s="6"/>
       <c r="R88" s="17"/>
       <c r="S88" s="6"/>
-      <c r="T88" s="17">
-        <v>1</v>
-      </c>
+      <c r="T88" s="17"/>
       <c r="V88" s="8" t="s">
         <v>136</v>
       </c>
@@ -49770,35 +49560,29 @@
     </row>
     <row r="89" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A89" s="10" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B89" s="17"/>
       <c r="C89" s="6"/>
       <c r="D89" s="17"/>
       <c r="E89" s="6"/>
-      <c r="F89" s="17">
-        <v>1</v>
-      </c>
+      <c r="F89" s="17"/>
       <c r="G89" s="6"/>
       <c r="H89" s="17"/>
-      <c r="I89" s="6">
-        <v>1</v>
-      </c>
-      <c r="J89" s="17">
-        <v>3</v>
-      </c>
+      <c r="I89" s="6"/>
+      <c r="J89" s="17"/>
       <c r="K89" s="6"/>
       <c r="L89" s="17"/>
-      <c r="M89" s="6">
-        <v>1</v>
-      </c>
+      <c r="M89" s="6"/>
       <c r="N89" s="17"/>
       <c r="O89" s="6"/>
       <c r="P89" s="17"/>
       <c r="Q89" s="6"/>
       <c r="R89" s="17"/>
       <c r="S89" s="6"/>
-      <c r="T89" s="17"/>
+      <c r="T89" s="17">
+        <v>2</v>
+      </c>
       <c r="V89" s="8" t="s">
         <v>136</v>
       </c>
@@ -49833,29 +49617,37 @@
     </row>
     <row r="90" spans="1:47" x14ac:dyDescent="0.45">
       <c r="A90" s="10" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B90" s="17"/>
       <c r="C90" s="6"/>
       <c r="D90" s="17"/>
-      <c r="E90" s="6"/>
-      <c r="F90" s="17"/>
+      <c r="E90" s="6">
+        <v>1</v>
+      </c>
+      <c r="F90" s="17">
+        <v>1</v>
+      </c>
       <c r="G90" s="6"/>
       <c r="H90" s="17"/>
       <c r="I90" s="6"/>
-      <c r="J90" s="17"/>
+      <c r="J90" s="17">
+        <v>7</v>
+      </c>
       <c r="K90" s="6"/>
       <c r="L90" s="17"/>
       <c r="M90" s="6"/>
-      <c r="N90" s="17"/>
+      <c r="N90" s="17">
+        <v>1</v>
+      </c>
       <c r="O90" s="6"/>
       <c r="P90" s="17"/>
       <c r="Q90" s="6"/>
-      <c r="R90" s="17"/>
+      <c r="R90" s="17">
+        <v>2</v>
+      </c>
       <c r="S90" s="6"/>
-      <c r="T90" s="17">
-        <v>2</v>
-      </c>
+      <c r="T90" s="17"/>
       <c r="V90" s="8" t="s">
         <v>136</v>
       </c>
@@ -49894,40 +49686,55 @@
         <v>156</v>
       </c>
     </row>
-    <row r="91" spans="1:47" x14ac:dyDescent="0.45">
-      <c r="A91" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B91" s="17"/>
-      <c r="C91" s="6"/>
-      <c r="D91" s="17"/>
-      <c r="E91" s="6">
-        <v>1</v>
-      </c>
-      <c r="F91" s="17">
-        <v>1</v>
-      </c>
-      <c r="G91" s="6"/>
-      <c r="H91" s="17"/>
-      <c r="I91" s="6"/>
-      <c r="J91" s="17">
-        <v>7</v>
-      </c>
-      <c r="K91" s="6"/>
-      <c r="L91" s="17"/>
-      <c r="M91" s="6"/>
-      <c r="N91" s="17">
-        <v>1</v>
-      </c>
-      <c r="O91" s="6"/>
-      <c r="P91" s="17"/>
-      <c r="Q91" s="6"/>
-      <c r="R91" s="17">
-        <v>2</v>
-      </c>
-      <c r="S91" s="6"/>
-      <c r="T91" s="17"/>
-      <c r="V91" s="8" t="s">
+    <row r="91" spans="1:47" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A91" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B91" s="18"/>
+      <c r="C91" s="19">
+        <v>2</v>
+      </c>
+      <c r="D91" s="18"/>
+      <c r="E91" s="19">
+        <v>1</v>
+      </c>
+      <c r="F91" s="18">
+        <v>2</v>
+      </c>
+      <c r="G91" s="19">
+        <v>3</v>
+      </c>
+      <c r="H91" s="18"/>
+      <c r="I91" s="19">
+        <v>3</v>
+      </c>
+      <c r="J91" s="18">
+        <v>3</v>
+      </c>
+      <c r="K91" s="19"/>
+      <c r="L91" s="18">
+        <v>3</v>
+      </c>
+      <c r="M91" s="19">
+        <v>2</v>
+      </c>
+      <c r="N91" s="18">
+        <v>4</v>
+      </c>
+      <c r="O91" s="19">
+        <v>1</v>
+      </c>
+      <c r="P91" s="18"/>
+      <c r="Q91" s="19"/>
+      <c r="R91" s="18">
+        <v>1</v>
+      </c>
+      <c r="S91" s="19"/>
+      <c r="T91" s="18">
+        <v>4</v>
+      </c>
+      <c r="U91" s="15"/>
+      <c r="V91" s="12" t="s">
         <v>136</v>
       </c>
       <c r="Z91" s="10" t="s">
@@ -49981,57 +49788,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="92" spans="1:47" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A92" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B92" s="18"/>
-      <c r="C92" s="19">
-        <v>2</v>
-      </c>
-      <c r="D92" s="18"/>
-      <c r="E92" s="19">
-        <v>1</v>
-      </c>
-      <c r="F92" s="18">
-        <v>2</v>
-      </c>
-      <c r="G92" s="19">
-        <v>3</v>
-      </c>
-      <c r="H92" s="18"/>
-      <c r="I92" s="19">
-        <v>3</v>
-      </c>
-      <c r="J92" s="18">
-        <v>3</v>
-      </c>
-      <c r="K92" s="19"/>
-      <c r="L92" s="18">
-        <v>3</v>
-      </c>
-      <c r="M92" s="19">
-        <v>2</v>
-      </c>
-      <c r="N92" s="18">
-        <v>4</v>
-      </c>
-      <c r="O92" s="19">
-        <v>1</v>
-      </c>
-      <c r="P92" s="18"/>
-      <c r="Q92" s="19"/>
-      <c r="R92" s="18">
-        <v>1</v>
-      </c>
-      <c r="S92" s="19"/>
-      <c r="T92" s="18">
-        <v>4</v>
-      </c>
-      <c r="U92" s="15"/>
-      <c r="V92" s="12" t="s">
-        <v>136</v>
-      </c>
+    <row r="92" spans="1:47" x14ac:dyDescent="0.45">
       <c r="Z92" s="10" t="s">
         <v>11</v>
       </c>
@@ -50327,42 +50084,38 @@
     </row>
     <row r="99" spans="26:47" x14ac:dyDescent="0.45">
       <c r="Z99" s="10" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="AA99" s="17"/>
-      <c r="AB99" s="6"/>
-      <c r="AC99" s="17">
-        <v>2</v>
-      </c>
+      <c r="AB99" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC99" s="17"/>
       <c r="AD99" s="6"/>
-      <c r="AE99" s="17">
-        <v>5</v>
-      </c>
+      <c r="AE99" s="17"/>
       <c r="AF99" s="6">
-        <v>4</v>
-      </c>
-      <c r="AG99" s="17">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AG99" s="17"/>
       <c r="AH99" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI99" s="17">
         <v>6</v>
       </c>
       <c r="AJ99" s="6"/>
-      <c r="AK99" s="17"/>
+      <c r="AK99" s="17">
+        <v>1</v>
+      </c>
       <c r="AL99" s="6"/>
-      <c r="AM99" s="17">
-        <v>8</v>
-      </c>
+      <c r="AM99" s="17"/>
       <c r="AN99" s="6"/>
       <c r="AO99" s="17"/>
       <c r="AP99" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ99" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR99" s="6"/>
       <c r="AS99" s="17">
@@ -50372,52 +50125,6 @@
         <v>1</v>
       </c>
       <c r="AU99" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="100" spans="26:47" x14ac:dyDescent="0.45">
-      <c r="Z100" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA100" s="17"/>
-      <c r="AB100" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC100" s="17"/>
-      <c r="AD100" s="6"/>
-      <c r="AE100" s="17"/>
-      <c r="AF100" s="6">
-        <v>2</v>
-      </c>
-      <c r="AG100" s="17"/>
-      <c r="AH100" s="6">
-        <v>1</v>
-      </c>
-      <c r="AI100" s="17">
-        <v>6</v>
-      </c>
-      <c r="AJ100" s="6"/>
-      <c r="AK100" s="17">
-        <v>1</v>
-      </c>
-      <c r="AL100" s="6"/>
-      <c r="AM100" s="17"/>
-      <c r="AN100" s="6"/>
-      <c r="AO100" s="17"/>
-      <c r="AP100" s="6">
-        <v>2</v>
-      </c>
-      <c r="AQ100" s="17">
-        <v>1</v>
-      </c>
-      <c r="AR100" s="6"/>
-      <c r="AS100" s="17">
-        <v>6</v>
-      </c>
-      <c r="AT100" s="14">
-        <v>1</v>
-      </c>
-      <c r="AU100" s="8" t="s">
         <v>123</v>
       </c>
     </row>
@@ -50428,46 +50135,46 @@
     </row>
     <row r="106" spans="26:47" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="Z106" s="9"/>
-      <c r="AA106" s="20">
-        <v>1</v>
-      </c>
-      <c r="AB106" s="21"/>
-      <c r="AC106" s="20">
-        <v>2</v>
-      </c>
-      <c r="AD106" s="21"/>
-      <c r="AE106" s="20">
-        <v>3</v>
-      </c>
-      <c r="AF106" s="21"/>
-      <c r="AG106" s="20">
-        <v>4</v>
-      </c>
-      <c r="AH106" s="21"/>
-      <c r="AI106" s="20">
+      <c r="AA106" s="22">
+        <v>1</v>
+      </c>
+      <c r="AB106" s="23"/>
+      <c r="AC106" s="22">
+        <v>2</v>
+      </c>
+      <c r="AD106" s="23"/>
+      <c r="AE106" s="22">
+        <v>3</v>
+      </c>
+      <c r="AF106" s="23"/>
+      <c r="AG106" s="22">
+        <v>4</v>
+      </c>
+      <c r="AH106" s="23"/>
+      <c r="AI106" s="22">
         <v>5</v>
       </c>
-      <c r="AJ106" s="21"/>
-      <c r="AK106" s="20">
+      <c r="AJ106" s="23"/>
+      <c r="AK106" s="22">
         <v>6</v>
       </c>
-      <c r="AL106" s="21"/>
-      <c r="AM106" s="20">
+      <c r="AL106" s="23"/>
+      <c r="AM106" s="22">
         <v>7</v>
       </c>
-      <c r="AN106" s="21"/>
-      <c r="AO106" s="20">
+      <c r="AN106" s="23"/>
+      <c r="AO106" s="22">
         <v>8</v>
       </c>
-      <c r="AP106" s="21"/>
-      <c r="AQ106" s="20">
+      <c r="AP106" s="23"/>
+      <c r="AQ106" s="22">
         <v>9</v>
       </c>
-      <c r="AR106" s="21"/>
-      <c r="AS106" s="20">
+      <c r="AR106" s="23"/>
+      <c r="AS106" s="22">
         <v>10</v>
       </c>
-      <c r="AT106" s="21"/>
+      <c r="AT106" s="23"/>
     </row>
     <row r="107" spans="26:47" x14ac:dyDescent="0.45">
       <c r="Z107" s="7" t="s">
@@ -50804,46 +50511,46 @@
     </row>
     <row r="118" spans="26:47" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="Z118" s="9"/>
-      <c r="AA118" s="20">
-        <v>1</v>
-      </c>
-      <c r="AB118" s="21"/>
-      <c r="AC118" s="20">
-        <v>2</v>
-      </c>
-      <c r="AD118" s="21"/>
-      <c r="AE118" s="20">
-        <v>3</v>
-      </c>
-      <c r="AF118" s="21"/>
-      <c r="AG118" s="20">
-        <v>4</v>
-      </c>
-      <c r="AH118" s="21"/>
-      <c r="AI118" s="20">
+      <c r="AA118" s="22">
+        <v>1</v>
+      </c>
+      <c r="AB118" s="23"/>
+      <c r="AC118" s="22">
+        <v>2</v>
+      </c>
+      <c r="AD118" s="23"/>
+      <c r="AE118" s="22">
+        <v>3</v>
+      </c>
+      <c r="AF118" s="23"/>
+      <c r="AG118" s="22">
+        <v>4</v>
+      </c>
+      <c r="AH118" s="23"/>
+      <c r="AI118" s="22">
         <v>5</v>
       </c>
-      <c r="AJ118" s="21"/>
-      <c r="AK118" s="20">
+      <c r="AJ118" s="23"/>
+      <c r="AK118" s="22">
         <v>6</v>
       </c>
-      <c r="AL118" s="21"/>
-      <c r="AM118" s="20">
+      <c r="AL118" s="23"/>
+      <c r="AM118" s="22">
         <v>7</v>
       </c>
-      <c r="AN118" s="21"/>
-      <c r="AO118" s="20">
+      <c r="AN118" s="23"/>
+      <c r="AO118" s="22">
         <v>8</v>
       </c>
-      <c r="AP118" s="21"/>
-      <c r="AQ118" s="20">
+      <c r="AP118" s="23"/>
+      <c r="AQ118" s="22">
         <v>9</v>
       </c>
-      <c r="AR118" s="21"/>
-      <c r="AS118" s="20">
+      <c r="AR118" s="23"/>
+      <c r="AS118" s="22">
         <v>10</v>
       </c>
-      <c r="AT118" s="21"/>
+      <c r="AT118" s="23"/>
     </row>
     <row r="119" spans="26:47" x14ac:dyDescent="0.45">
       <c r="Z119" s="7" t="s">
@@ -51347,18 +51054,68 @@
     </sortState>
   </autoFilter>
   <mergeCells count="90">
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="AK118:AL118"/>
+    <mergeCell ref="AM118:AN118"/>
+    <mergeCell ref="AO118:AP118"/>
+    <mergeCell ref="AQ118:AR118"/>
+    <mergeCell ref="AS118:AT118"/>
+    <mergeCell ref="AA118:AB118"/>
+    <mergeCell ref="AC118:AD118"/>
+    <mergeCell ref="AE118:AF118"/>
+    <mergeCell ref="AG118:AH118"/>
+    <mergeCell ref="AI118:AJ118"/>
+    <mergeCell ref="AK106:AL106"/>
+    <mergeCell ref="AM106:AN106"/>
+    <mergeCell ref="AO106:AP106"/>
+    <mergeCell ref="AQ106:AR106"/>
+    <mergeCell ref="AS106:AT106"/>
+    <mergeCell ref="AA106:AB106"/>
+    <mergeCell ref="AC106:AD106"/>
+    <mergeCell ref="AE106:AF106"/>
+    <mergeCell ref="AG106:AH106"/>
+    <mergeCell ref="AI106:AJ106"/>
+    <mergeCell ref="AK84:AL84"/>
+    <mergeCell ref="AM84:AN84"/>
+    <mergeCell ref="AO84:AP84"/>
+    <mergeCell ref="AQ84:AR84"/>
+    <mergeCell ref="AS84:AT84"/>
+    <mergeCell ref="AA84:AB84"/>
+    <mergeCell ref="AC84:AD84"/>
+    <mergeCell ref="AE84:AF84"/>
+    <mergeCell ref="AG84:AH84"/>
+    <mergeCell ref="AI84:AJ84"/>
+    <mergeCell ref="AA68:AB68"/>
+    <mergeCell ref="AC68:AD68"/>
+    <mergeCell ref="AE68:AF68"/>
+    <mergeCell ref="AG68:AH68"/>
+    <mergeCell ref="AI68:AJ68"/>
+    <mergeCell ref="AK55:AL55"/>
+    <mergeCell ref="AM55:AN55"/>
+    <mergeCell ref="AO55:AP55"/>
+    <mergeCell ref="AQ68:AR68"/>
+    <mergeCell ref="AS68:AT68"/>
+    <mergeCell ref="AQ55:AR55"/>
+    <mergeCell ref="AS55:AT55"/>
+    <mergeCell ref="AK68:AL68"/>
+    <mergeCell ref="AM68:AN68"/>
+    <mergeCell ref="AO68:AP68"/>
+    <mergeCell ref="AA55:AB55"/>
+    <mergeCell ref="AC55:AD55"/>
+    <mergeCell ref="AE55:AF55"/>
+    <mergeCell ref="AG55:AH55"/>
+    <mergeCell ref="AI55:AJ55"/>
+    <mergeCell ref="AQ26:AR26"/>
+    <mergeCell ref="AS26:AT26"/>
+    <mergeCell ref="AA40:AB40"/>
+    <mergeCell ref="AC40:AD40"/>
+    <mergeCell ref="AE40:AF40"/>
+    <mergeCell ref="AG40:AH40"/>
+    <mergeCell ref="AI40:AJ40"/>
+    <mergeCell ref="AK40:AL40"/>
+    <mergeCell ref="AM40:AN40"/>
+    <mergeCell ref="AO40:AP40"/>
+    <mergeCell ref="AQ40:AR40"/>
+    <mergeCell ref="AS40:AT40"/>
     <mergeCell ref="AQ1:AR1"/>
     <mergeCell ref="AS1:AT1"/>
     <mergeCell ref="AA26:AB26"/>
@@ -51375,68 +51132,18 @@
     <mergeCell ref="AK1:AL1"/>
     <mergeCell ref="AM1:AN1"/>
     <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="AQ26:AR26"/>
-    <mergeCell ref="AS26:AT26"/>
-    <mergeCell ref="AA40:AB40"/>
-    <mergeCell ref="AC40:AD40"/>
-    <mergeCell ref="AE40:AF40"/>
-    <mergeCell ref="AG40:AH40"/>
-    <mergeCell ref="AI40:AJ40"/>
-    <mergeCell ref="AK40:AL40"/>
-    <mergeCell ref="AM40:AN40"/>
-    <mergeCell ref="AO40:AP40"/>
-    <mergeCell ref="AQ40:AR40"/>
-    <mergeCell ref="AS40:AT40"/>
-    <mergeCell ref="AA55:AB55"/>
-    <mergeCell ref="AC55:AD55"/>
-    <mergeCell ref="AE55:AF55"/>
-    <mergeCell ref="AG55:AH55"/>
-    <mergeCell ref="AI55:AJ55"/>
-    <mergeCell ref="AK55:AL55"/>
-    <mergeCell ref="AM55:AN55"/>
-    <mergeCell ref="AO55:AP55"/>
-    <mergeCell ref="AQ68:AR68"/>
-    <mergeCell ref="AS68:AT68"/>
-    <mergeCell ref="AQ55:AR55"/>
-    <mergeCell ref="AS55:AT55"/>
-    <mergeCell ref="AK68:AL68"/>
-    <mergeCell ref="AM68:AN68"/>
-    <mergeCell ref="AO68:AP68"/>
-    <mergeCell ref="AA68:AB68"/>
-    <mergeCell ref="AC68:AD68"/>
-    <mergeCell ref="AE68:AF68"/>
-    <mergeCell ref="AG68:AH68"/>
-    <mergeCell ref="AI68:AJ68"/>
-    <mergeCell ref="AA84:AB84"/>
-    <mergeCell ref="AC84:AD84"/>
-    <mergeCell ref="AE84:AF84"/>
-    <mergeCell ref="AG84:AH84"/>
-    <mergeCell ref="AI84:AJ84"/>
-    <mergeCell ref="AK84:AL84"/>
-    <mergeCell ref="AM84:AN84"/>
-    <mergeCell ref="AO84:AP84"/>
-    <mergeCell ref="AQ84:AR84"/>
-    <mergeCell ref="AS84:AT84"/>
-    <mergeCell ref="AA106:AB106"/>
-    <mergeCell ref="AC106:AD106"/>
-    <mergeCell ref="AE106:AF106"/>
-    <mergeCell ref="AG106:AH106"/>
-    <mergeCell ref="AI106:AJ106"/>
-    <mergeCell ref="AK106:AL106"/>
-    <mergeCell ref="AM106:AN106"/>
-    <mergeCell ref="AO106:AP106"/>
-    <mergeCell ref="AQ106:AR106"/>
-    <mergeCell ref="AS106:AT106"/>
-    <mergeCell ref="AA118:AB118"/>
-    <mergeCell ref="AC118:AD118"/>
-    <mergeCell ref="AE118:AF118"/>
-    <mergeCell ref="AG118:AH118"/>
-    <mergeCell ref="AI118:AJ118"/>
-    <mergeCell ref="AK118:AL118"/>
-    <mergeCell ref="AM118:AN118"/>
-    <mergeCell ref="AO118:AP118"/>
-    <mergeCell ref="AQ118:AR118"/>
-    <mergeCell ref="AS118:AT118"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="AA1:AB1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
